--- a/Marathon_Training_Log.xlsx
+++ b/Marathon_Training_Log.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\prsap\Dropbox (Personal)\Personal\Marathon Training\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Coursework\24-Git_Projects\02-Marathon_Training_Personal\Marathon_Training\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D9CA19E-2000-4942-AA0F-DE6512AB4371}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB9C8120-823B-4D29-A36A-74DFEFAD3694}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Log" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="74">
   <si>
     <t>Marathon Training Log — Pre-Super Base</t>
   </si>
@@ -254,6 +254,12 @@
   </si>
   <si>
     <t>There are no pace targets in this block by design — run everything by feel. Pace/HR should be LOGGED for your own trend-tracking, not used as a target.</t>
+  </si>
+  <si>
+    <t>10 min Pre-Run Warm Up with Matt Wilpers + 30 min Tempo Run with Matt Wilpers</t>
+  </si>
+  <si>
+    <t>Completed additiona 35 min run with Apple watch. Heart rate did not actually reflect RPE. Slightly hot weather and mix of hills.</t>
   </si>
 </sst>
 </file>
@@ -369,7 +375,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -417,6 +423,12 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -685,17 +697,19 @@
   <dimension ref="B2:P61"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="15.5703125" customWidth="1"/>
-    <col min="3" max="3" width="18" customWidth="1"/>
-    <col min="4" max="4" width="25" customWidth="1"/>
-    <col min="5" max="5" width="16" customWidth="1"/>
-    <col min="6" max="6" width="34" customWidth="1"/>
-    <col min="7" max="7" width="16" customWidth="1"/>
-    <col min="8" max="10" width="11" customWidth="1"/>
-    <col min="11" max="11" width="9" customWidth="1"/>
-    <col min="12" max="14" width="10" customWidth="1"/>
-    <col min="15" max="15" width="9" customWidth="1"/>
-    <col min="16" max="16" width="32" customWidth="1"/>
+    <col min="2" max="2" width="43.140625" customWidth="1"/>
+    <col min="3" max="3" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="3.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="111" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="71.5703125" customWidth="1"/>
+    <col min="8" max="8" width="7.7109375" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="8" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="7.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="43.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -703,11 +717,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="2" t="s">
+    <row r="3" spans="2:16" s="21" customFormat="1" ht="26.25" x14ac:dyDescent="0.25">
+      <c r="B3" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="20" t="s">
         <v>2</v>
       </c>
     </row>
@@ -758,7 +772,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="4">
         <v>46230</v>
       </c>
@@ -774,20 +788,36 @@
       <c r="F6" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="G6" s="7"/>
+      <c r="G6" s="7" t="s">
+        <v>72</v>
+      </c>
       <c r="H6" s="8" t="s">
         <v>21</v>
       </c>
       <c r="I6" s="5">
         <v>65</v>
       </c>
-      <c r="J6" s="8"/>
-      <c r="K6" s="8"/>
-      <c r="L6" s="8"/>
-      <c r="M6" s="8"/>
-      <c r="N6" s="8"/>
-      <c r="O6" s="8"/>
-      <c r="P6" s="7"/>
+      <c r="J6" s="8">
+        <v>65</v>
+      </c>
+      <c r="K6" s="8">
+        <v>5.01</v>
+      </c>
+      <c r="L6" s="8">
+        <v>12.97</v>
+      </c>
+      <c r="M6" s="8">
+        <v>171</v>
+      </c>
+      <c r="N6" s="8">
+        <v>178</v>
+      </c>
+      <c r="O6" s="8">
+        <v>5</v>
+      </c>
+      <c r="P6" s="7" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="7" spans="2:16" ht="51.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="9">
@@ -2554,11 +2584,11 @@
       </c>
       <c r="D6" s="15">
         <f>SUMIFS(Log!$J$6:$J$61,Log!$D$6:$D$61,B6)</f>
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="E6" s="15">
         <f>SUMIFS(Log!$K$6:$K$61,Log!$D$6:$D$61,B6)</f>
-        <v>0</v>
+        <v>5.01</v>
       </c>
       <c r="F6" s="15" t="str">
         <f>IFERROR(AVERAGEIFS(Log!$O$6:$O$61,Log!$D$6:$D$61,B6,Log!$H$6:$H$61,"Done"),"")</f>
@@ -2722,11 +2752,11 @@
       </c>
       <c r="D14" s="17">
         <f>SUM(D6:D13)</f>
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="E14" s="17">
         <f>SUM(E6:E13)</f>
-        <v>0</v>
+        <v>5.01</v>
       </c>
     </row>
   </sheetData>

--- a/Marathon_Training_Log.xlsx
+++ b/Marathon_Training_Log.xlsx
@@ -1,19 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
-  <fileVersion appName="Calc" lowestEdited="4"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Coursework\24-Git_Projects\02-Marathon_Training_Personal\Marathon_Training\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E872A67B-7BA3-4853-A146-5E5F12D5872C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Log" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="Weekly Summary" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="Session Guide" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="Log" sheetId="1" r:id="rId1"/>
+    <sheet name="Weekly Summary" sheetId="2" r:id="rId2"/>
+    <sheet name="Session Guide" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="ExcelA1"/>
     </ext>
@@ -22,242 +38,252 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="268" uniqueCount="75">
-  <si>
-    <t xml:space="preserve">Marathon Training Log — Pre-Super Base</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stablemaster's Method (John Starrett). Yellow cells are yours to fill in after each session.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yellow = your input after the run. Example: Actual Duration 66, Distance 4.7, Avg Pace 14:02, Avg HR 148, Max HR 161, RPE 5.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Date</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Day</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wk</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Session Type</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Planned Workout</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Peloton Class Used</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Planned Duration (min)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Actual Duration (min)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Distance (mi)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avg Pace (min/mi)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avg HR (bpm)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Max HR (bpm)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RPE / Felt (1-10)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Notes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Easy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Easy run 65 min — conversational effort, nose-breathing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10 min Pre-Run Warm Up with Matt Wilpers + 30 min Tempo Run with Matt Wilpers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Done</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Completed additiona 35 min run with Apple watch. Heart rate did not actually reflect RPE. Slightly hot weather and mix of hills.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tue</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Key – Strides</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KEY: WU + 3x(5x20s @ 5K effort, jog back) w/ 3 min jog between sets + CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Planned</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Wed</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rest</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rest / cross-train (easy bike/swim optional)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Thu</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Easy run 45-50 min (or rest if legs heavy from Tue)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fri</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Key – Hills</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KEY: WU + drills + 4x 8-sec blasts (2:30 min walk recovery)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sat</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Long</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Long run 90 min easy — no tempo, conversational</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sun</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KEY: WU + 3x(5x30s @ 5K effort, jog back) w/ 3 min jog between sets + CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Easy run 45-50 min (or rest if legs heavy from Wed)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Key – Hills+Long</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KEY: WU + drills + 4x 8-sec blasts (2:30 min walk recovery) — film your form  |  + Long run 90 min easy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KEY: WU + 3x(5x40s @ 5K effort, jog back) w/ 3 min jog between sets + CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KEY: WU + drills + 6x 8-sec blasts (2:30 min walk recovery)  |  + Long run 90 min easy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KEY: WU + 3x(5x40s) + 3 min jog + 2 min @ 5K effort add-on + CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KEY: WU + 3x(5x40s) + 3 min jog + 3 min @ 5K effort add-on + CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KEY: WU + drills + 8x 8-sec blasts (2:30 min walk recovery)  |  + Long run 90 min easy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KEY: WU + 3x(5x40s) + 3 min jog + 4 min @ 5K effort add-on + CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KEY: WU + 3x(5x40s) + 3 min jog + 5 min @ 5K effort add-on + CD (peak session)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">KEY: Repeat: WU + 3x(5x40s) + 3 min jog + 5 min add-on + CD (consolidate — form dialled in)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Weekly Summary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Auto-calculated from the Log sheet — nothing to fill in here.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sessions Logged</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total Actual Minutes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total Distance (mi)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Avg RPE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Block total</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Session Guide — Pre-Super Base (Stablemaster's Method)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Quick reference. Full detail lives in your Foundation &amp; Pre-Super Base workbook's Workout Library tab.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Easy Run (Mon, 65 min)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Conversational effort, full sentences, nose-breathing if possible. Peloton: any easy/'fun run' or Zone 2 tread class of matching length — ignore output/pace pushes, run by feel.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Easy Run (Thu, 45-50 min)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Same easy effort, shorter. Skip or shorten if legs are heavy from Tue strides or the upcoming Fri hill session.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aerobic Strides (Tue, KEY)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reps at ~5K effort to a landmark, jog back, big recovery between sets. Peloton: use a class for the warm-up/cool-down only, then pause it and self-control the treadmill for the rep timing — no canned class matches this exact protocol.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hill Blasts (Fri or Sat, KEY)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8-sec near-max effort on a shallow incline (~5%), 2:30 WALK recovery between reps. Mantra: tall / relaxed / piston / pop. Week 1: Friday (own day). From week 2 on: same day as the long run (Saturday), done first, before the long run. Peloton: use a class for warm-up music/voice, then pause it and control incline/timing yourself — no canned class matches this protocol.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Long Run (Saturday, 90 min)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Anchored on Saturday every week per your preference. Stays at 90 min all block — easy, conversational, no tempo. From week 2 on it follows straight after hill blasts on the same day; week 1 only, it's a standalone Saturday session since hill blasts landed on Friday that week. Great one to run alongside a full-length Peloton easy/scenic tread class.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rest / Cross-train</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Full rest, walk, or easy low-impact cardio (bike/swim). Never turn it into a secret run.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Effort guide</t>
-  </si>
-  <si>
-    <t xml:space="preserve">There are no pace targets in this block by design — run everything by feel. Pace/HR should be LOGGED for your own trend-tracking, not used as a target.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="77">
+  <si>
+    <t>Marathon Training Log — Pre-Super Base</t>
+  </si>
+  <si>
+    <t>Stablemaster's Method (John Starrett). Yellow cells are yours to fill in after each session.</t>
+  </si>
+  <si>
+    <t>Yellow = your input after the run. Example: Actual Duration 66, Distance 4.7, Avg Pace 14:02, Avg HR 148, Max HR 161, RPE 5.</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Day</t>
+  </si>
+  <si>
+    <t>Wk</t>
+  </si>
+  <si>
+    <t>Session Type</t>
+  </si>
+  <si>
+    <t>Planned Workout</t>
+  </si>
+  <si>
+    <t>Peloton Class Used</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Planned Duration (min)</t>
+  </si>
+  <si>
+    <t>Actual Duration (min)</t>
+  </si>
+  <si>
+    <t>Distance (mi)</t>
+  </si>
+  <si>
+    <t>Avg Pace (min/mi)</t>
+  </si>
+  <si>
+    <t>Avg HR (bpm)</t>
+  </si>
+  <si>
+    <t>Max HR (bpm)</t>
+  </si>
+  <si>
+    <t>RPE / Felt (1-10)</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>Mon</t>
+  </si>
+  <si>
+    <t>Easy</t>
+  </si>
+  <si>
+    <t>Easy run 65 min — conversational effort, nose-breathing</t>
+  </si>
+  <si>
+    <t>10 min Pre-Run Warm Up with Matt Wilpers + 30 min Tempo Run with Matt Wilpers</t>
+  </si>
+  <si>
+    <t>Done</t>
+  </si>
+  <si>
+    <t>Completed additiona 35 min run with Apple watch. Heart rate did not actually reflect RPE. Slightly hot weather and mix of hills.</t>
+  </si>
+  <si>
+    <t>Tue</t>
+  </si>
+  <si>
+    <t>Key – Strides</t>
+  </si>
+  <si>
+    <t>KEY: WU + 3x(5x20s @ 5K effort, jog back) w/ 3 min jog between sets + CD</t>
+  </si>
+  <si>
+    <t>Planned</t>
+  </si>
+  <si>
+    <t>Wed</t>
+  </si>
+  <si>
+    <t>Rest</t>
+  </si>
+  <si>
+    <t>Rest / cross-train (easy bike/swim optional)</t>
+  </si>
+  <si>
+    <t>Thu</t>
+  </si>
+  <si>
+    <t>Easy run 45-50 min (or rest if legs heavy from Tue)</t>
+  </si>
+  <si>
+    <t>Fri</t>
+  </si>
+  <si>
+    <t>Key – Hills</t>
+  </si>
+  <si>
+    <t>KEY: WU + drills + 4x 8-sec blasts (2:30 min walk recovery)</t>
+  </si>
+  <si>
+    <t>Sat</t>
+  </si>
+  <si>
+    <t>Long</t>
+  </si>
+  <si>
+    <t>Long run 90 min easy — no tempo, conversational</t>
+  </si>
+  <si>
+    <t>Sun</t>
+  </si>
+  <si>
+    <t>KEY: WU + 3x(5x30s @ 5K effort, jog back) w/ 3 min jog between sets + CD</t>
+  </si>
+  <si>
+    <t>Easy run 45-50 min (or rest if legs heavy from Wed)</t>
+  </si>
+  <si>
+    <t>Key – Hills+Long</t>
+  </si>
+  <si>
+    <t>KEY: WU + drills + 4x 8-sec blasts (2:30 min walk recovery) — film your form  |  + Long run 90 min easy</t>
+  </si>
+  <si>
+    <t>KEY: WU + 3x(5x40s @ 5K effort, jog back) w/ 3 min jog between sets + CD</t>
+  </si>
+  <si>
+    <t>KEY: WU + drills + 6x 8-sec blasts (2:30 min walk recovery)  |  + Long run 90 min easy</t>
+  </si>
+  <si>
+    <t>KEY: WU + 3x(5x40s) + 3 min jog + 2 min @ 5K effort add-on + CD</t>
+  </si>
+  <si>
+    <t>KEY: WU + 3x(5x40s) + 3 min jog + 3 min @ 5K effort add-on + CD</t>
+  </si>
+  <si>
+    <t>KEY: WU + drills + 8x 8-sec blasts (2:30 min walk recovery)  |  + Long run 90 min easy</t>
+  </si>
+  <si>
+    <t>KEY: WU + 3x(5x40s) + 3 min jog + 4 min @ 5K effort add-on + CD</t>
+  </si>
+  <si>
+    <t>KEY: WU + 3x(5x40s) + 3 min jog + 5 min @ 5K effort add-on + CD (peak session)</t>
+  </si>
+  <si>
+    <t>KEY: Repeat: WU + 3x(5x40s) + 3 min jog + 5 min add-on + CD (consolidate — form dialled in)</t>
+  </si>
+  <si>
+    <t>Weekly Summary</t>
+  </si>
+  <si>
+    <t>Auto-calculated from the Log sheet — nothing to fill in here.</t>
+  </si>
+  <si>
+    <t>Sessions Logged</t>
+  </si>
+  <si>
+    <t>Total Actual Minutes</t>
+  </si>
+  <si>
+    <t>Total Distance (mi)</t>
+  </si>
+  <si>
+    <t>Avg RPE</t>
+  </si>
+  <si>
+    <t>Block total</t>
+  </si>
+  <si>
+    <t>Session Guide — Pre-Super Base (Stablemaster's Method)</t>
+  </si>
+  <si>
+    <t>Quick reference. Full detail lives in your Foundation &amp; Pre-Super Base workbook's Workout Library tab.</t>
+  </si>
+  <si>
+    <t>Easy Run (Mon, 65 min)</t>
+  </si>
+  <si>
+    <t>Conversational effort, full sentences, nose-breathing if possible. Peloton: any easy/'fun run' or Zone 2 tread class of matching length — ignore output/pace pushes, run by feel.</t>
+  </si>
+  <si>
+    <t>Easy Run (Thu, 45-50 min)</t>
+  </si>
+  <si>
+    <t>Same easy effort, shorter. Skip or shorten if legs are heavy from Tue strides or the upcoming Fri hill session.</t>
+  </si>
+  <si>
+    <t>Aerobic Strides (Tue, KEY)</t>
+  </si>
+  <si>
+    <t>Reps at ~5K effort to a landmark, jog back, big recovery between sets. Peloton: use a class for the warm-up/cool-down only, then pause it and self-control the treadmill for the rep timing — no canned class matches this exact protocol.</t>
+  </si>
+  <si>
+    <t>Hill Blasts (Fri or Sat, KEY)</t>
+  </si>
+  <si>
+    <t>8-sec near-max effort on a shallow incline (~5%), 2:30 WALK recovery between reps. Mantra: tall / relaxed / piston / pop. Week 1: Friday (own day). From week 2 on: same day as the long run (Saturday), done first, before the long run. Peloton: use a class for warm-up music/voice, then pause it and control incline/timing yourself — no canned class matches this protocol.</t>
+  </si>
+  <si>
+    <t>Long Run (Saturday, 90 min)</t>
+  </si>
+  <si>
+    <t>Anchored on Saturday every week per your preference. Stays at 90 min all block — easy, conversational, no tempo. From week 2 on it follows straight after hill blasts on the same day; week 1 only, it's a standalone Saturday session since hill blasts landed on Friday that week. Great one to run alongside a full-length Peloton easy/scenic tread class.</t>
+  </si>
+  <si>
+    <t>Rest / Cross-train</t>
+  </si>
+  <si>
+    <t>Full rest, walk, or easy low-impact cardio (bike/swim). Never turn it into a secret run.</t>
+  </si>
+  <si>
+    <t>Effort guide</t>
+  </si>
+  <si>
+    <t>There are no pace targets in this block by design — run everything by feel. Pace/HR should be LOGGED for your own trend-tracking, not used as a target.</t>
+  </si>
+  <si>
+    <t>10 min Pre-Run Warm Up + 45 min Marathon Race Prep (Becs Gentry) followed by 5 min stretch.</t>
+  </si>
+  <si>
+    <t>5x20 @5K effort &gt; 20 sec run + 1 min jog at 4 min/mile
+Speeds: 6.5/6.7/6.2
+Incline: 0.5/1/0
+First 10 min warmup + last remaining cooldown walk.
+Heart rate was jumping. But maintained conversational pace in between. Cooldown/recovery saw a heartrate drop of around 10-15 bpm from the Max.
+Used treadmill.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="mm/dd/yy&quot; (&quot;ddd\)"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="mm/dd/yy&quot; (&quot;ddd\)"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -266,62 +292,41 @@
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
+      <b/>
       <sz val="16"/>
       <color rgb="FF1F3A5F"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <i val="true"/>
+      <i/>
       <sz val="10"/>
       <color rgb="FF43597A"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="10"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
+      <b/>
       <sz val="11"/>
       <name val="Arial"/>
-      <family val="0"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -358,14 +363,14 @@
     </fill>
   </fills>
   <borders count="2">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left style="thin">
         <color rgb="FFD3DBE6"/>
       </left>
@@ -381,129 +386,70 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="22">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="164" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="FF000000"/>
@@ -562,13 +508,29 @@
       <rgbColor rgb="FF993366"/>
       <rgbColor rgb="FF333399"/>
       <rgbColor rgb="FF333333"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
     </indexedColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -610,12 +572,12 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -644,7 +606,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -665,7 +627,7 @@
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
@@ -716,7 +678,7 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
@@ -734,42 +696,41 @@
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
+          <a:tileRect/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:P61"/>
-  <sheetFormatPr defaultColWidth="8.71484375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="43.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="4.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="3.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="15.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="111"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="71.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="7.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="9.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="7.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="7.15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="43.42"/>
+    <col min="2" max="2" width="43.140625" customWidth="1"/>
+    <col min="3" max="3" width="4.85546875" customWidth="1"/>
+    <col min="4" max="4" width="3.85546875" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" customWidth="1"/>
+    <col min="6" max="6" width="111" customWidth="1"/>
+    <col min="7" max="7" width="71.5703125" customWidth="1"/>
+    <col min="8" max="8" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="9.5703125" customWidth="1"/>
+    <col min="13" max="13" width="7.5703125" customWidth="1"/>
+    <col min="14" max="14" width="8" customWidth="1"/>
+    <col min="15" max="15" width="7.140625" customWidth="1"/>
+    <col min="16" max="16" width="73.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" spans="2:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" s="2" customFormat="true" ht="26.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" spans="2:16" s="2" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
@@ -777,7 +738,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" spans="2:16" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
         <v>3</v>
       </c>
@@ -824,14 +785,14 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="38.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="5" t="n">
+    <row r="6" spans="2:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="5">
         <v>46230</v>
       </c>
       <c r="C6" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D6" s="6" t="n">
+      <c r="D6" s="6">
         <v>1</v>
       </c>
       <c r="E6" s="6" t="s">
@@ -846,39 +807,39 @@
       <c r="H6" s="9" t="s">
         <v>22</v>
       </c>
-      <c r="I6" s="6" t="n">
+      <c r="I6" s="6">
         <v>65</v>
       </c>
-      <c r="J6" s="9" t="n">
+      <c r="J6" s="9">
         <v>65</v>
       </c>
-      <c r="K6" s="9" t="n">
+      <c r="K6" s="9">
         <v>5.01</v>
       </c>
-      <c r="L6" s="9" t="n">
+      <c r="L6" s="9">
         <v>12.97</v>
       </c>
-      <c r="M6" s="9" t="n">
+      <c r="M6" s="9">
         <v>171</v>
       </c>
-      <c r="N6" s="9" t="n">
+      <c r="N6" s="9">
         <v>178</v>
       </c>
-      <c r="O6" s="9" t="n">
+      <c r="O6" s="9">
         <v>5</v>
       </c>
       <c r="P6" s="8" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="51.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="10" t="n">
+    <row r="7" spans="2:16" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="10">
         <v>46231</v>
       </c>
       <c r="C7" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="D7" s="11" t="n">
+      <c r="D7" s="11">
         <v>1</v>
       </c>
       <c r="E7" s="11" t="s">
@@ -887,29 +848,45 @@
       <c r="F7" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="G7" s="8"/>
+      <c r="G7" s="8" t="s">
+        <v>75</v>
+      </c>
       <c r="H7" s="9" t="s">
-        <v>27</v>
-      </c>
-      <c r="I7" s="11" t="n">
+        <v>22</v>
+      </c>
+      <c r="I7" s="11">
         <v>50</v>
       </c>
-      <c r="J7" s="9"/>
-      <c r="K7" s="9"/>
-      <c r="L7" s="9"/>
-      <c r="M7" s="9"/>
-      <c r="N7" s="9"/>
-      <c r="O7" s="9"/>
-      <c r="P7" s="8"/>
-    </row>
-    <row r="8" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="13" t="n">
+      <c r="J7" s="9">
+        <v>55</v>
+      </c>
+      <c r="K7" s="9">
+        <v>2.8</v>
+      </c>
+      <c r="L7" s="9">
+        <v>3.7</v>
+      </c>
+      <c r="M7" s="9">
+        <v>144</v>
+      </c>
+      <c r="N7" s="9">
+        <v>176</v>
+      </c>
+      <c r="O7" s="9">
+        <v>6</v>
+      </c>
+      <c r="P7" s="8" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="8" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="13">
         <v>46232</v>
       </c>
       <c r="C8" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="14" t="n">
+      <c r="D8" s="14">
         <v>1</v>
       </c>
       <c r="E8" s="14" t="s">
@@ -922,7 +899,7 @@
       <c r="H8" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="I8" s="14" t="n">
+      <c r="I8" s="14">
         <v>0</v>
       </c>
       <c r="J8" s="9"/>
@@ -933,14 +910,14 @@
       <c r="O8" s="9"/>
       <c r="P8" s="8"/>
     </row>
-    <row r="9" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="5" t="n">
+    <row r="9" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="5">
         <v>46233</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="6" t="n">
+      <c r="D9" s="6">
         <v>1</v>
       </c>
       <c r="E9" s="6" t="s">
@@ -953,7 +930,7 @@
       <c r="H9" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="I9" s="6" t="n">
+      <c r="I9" s="6">
         <v>50</v>
       </c>
       <c r="J9" s="9"/>
@@ -964,14 +941,14 @@
       <c r="O9" s="9"/>
       <c r="P9" s="8"/>
     </row>
-    <row r="10" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="10" t="n">
+    <row r="10" spans="2:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="10">
         <v>46234</v>
       </c>
       <c r="C10" s="11" t="s">
         <v>33</v>
       </c>
-      <c r="D10" s="11" t="n">
+      <c r="D10" s="11">
         <v>1</v>
       </c>
       <c r="E10" s="11" t="s">
@@ -984,7 +961,7 @@
       <c r="H10" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="I10" s="11" t="n">
+      <c r="I10" s="11">
         <v>45</v>
       </c>
       <c r="J10" s="9"/>
@@ -995,14 +972,14 @@
       <c r="O10" s="9"/>
       <c r="P10" s="8"/>
     </row>
-    <row r="11" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="10" t="n">
+    <row r="11" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="10">
         <v>46235</v>
       </c>
       <c r="C11" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="D11" s="11" t="n">
+      <c r="D11" s="11">
         <v>1</v>
       </c>
       <c r="E11" s="11" t="s">
@@ -1015,7 +992,7 @@
       <c r="H11" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="I11" s="11" t="n">
+      <c r="I11" s="11">
         <v>90</v>
       </c>
       <c r="J11" s="9"/>
@@ -1026,14 +1003,14 @@
       <c r="O11" s="9"/>
       <c r="P11" s="8"/>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="13" t="n">
+    <row r="12" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="13">
         <v>46236</v>
       </c>
       <c r="C12" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="D12" s="14" t="n">
+      <c r="D12" s="14">
         <v>1</v>
       </c>
       <c r="E12" s="14" t="s">
@@ -1046,7 +1023,7 @@
       <c r="H12" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="I12" s="14" t="n">
+      <c r="I12" s="14">
         <v>0</v>
       </c>
       <c r="J12" s="9"/>
@@ -1057,14 +1034,14 @@
       <c r="O12" s="9"/>
       <c r="P12" s="8"/>
     </row>
-    <row r="13" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="13" t="n">
+    <row r="13" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="13">
         <v>46237</v>
       </c>
       <c r="C13" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="D13" s="14" t="n">
+      <c r="D13" s="14">
         <v>2</v>
       </c>
       <c r="E13" s="14" t="s">
@@ -1077,7 +1054,7 @@
       <c r="H13" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="I13" s="14" t="n">
+      <c r="I13" s="14">
         <v>0</v>
       </c>
       <c r="J13" s="9"/>
@@ -1088,14 +1065,14 @@
       <c r="O13" s="9"/>
       <c r="P13" s="8"/>
     </row>
-    <row r="14" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="5" t="n">
+    <row r="14" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="5">
         <v>46238</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D14" s="6" t="n">
+      <c r="D14" s="6">
         <v>2</v>
       </c>
       <c r="E14" s="6" t="s">
@@ -1108,7 +1085,7 @@
       <c r="H14" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="I14" s="6" t="n">
+      <c r="I14" s="6">
         <v>65</v>
       </c>
       <c r="J14" s="9"/>
@@ -1119,14 +1096,14 @@
       <c r="O14" s="9"/>
       <c r="P14" s="8"/>
     </row>
-    <row r="15" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B15" s="10" t="n">
+    <row r="15" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="10">
         <v>46239</v>
       </c>
       <c r="C15" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="D15" s="11" t="n">
+      <c r="D15" s="11">
         <v>2</v>
       </c>
       <c r="E15" s="11" t="s">
@@ -1139,7 +1116,7 @@
       <c r="H15" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="I15" s="11" t="n">
+      <c r="I15" s="11">
         <v>52</v>
       </c>
       <c r="J15" s="9"/>
@@ -1150,14 +1127,14 @@
       <c r="O15" s="9"/>
       <c r="P15" s="8"/>
     </row>
-    <row r="16" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B16" s="13" t="n">
+    <row r="16" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="13">
         <v>46240</v>
       </c>
       <c r="C16" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="D16" s="14" t="n">
+      <c r="D16" s="14">
         <v>2</v>
       </c>
       <c r="E16" s="14" t="s">
@@ -1170,7 +1147,7 @@
       <c r="H16" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="I16" s="14" t="n">
+      <c r="I16" s="14">
         <v>0</v>
       </c>
       <c r="J16" s="9"/>
@@ -1181,14 +1158,14 @@
       <c r="O16" s="9"/>
       <c r="P16" s="8"/>
     </row>
-    <row r="17" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B17" s="5" t="n">
+    <row r="17" spans="2:16" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B17" s="5">
         <v>46241</v>
       </c>
       <c r="C17" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D17" s="6" t="n">
+      <c r="D17" s="6">
         <v>2</v>
       </c>
       <c r="E17" s="6" t="s">
@@ -1201,7 +1178,7 @@
       <c r="H17" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="I17" s="6" t="n">
+      <c r="I17" s="6">
         <v>50</v>
       </c>
       <c r="J17" s="9"/>
@@ -1212,14 +1189,14 @@
       <c r="O17" s="9"/>
       <c r="P17" s="8"/>
     </row>
-    <row r="18" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B18" s="10" t="n">
+    <row r="18" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B18" s="10">
         <v>46242</v>
       </c>
       <c r="C18" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="D18" s="11" t="n">
+      <c r="D18" s="11">
         <v>2</v>
       </c>
       <c r="E18" s="11" t="s">
@@ -1232,7 +1209,7 @@
       <c r="H18" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="I18" s="11" t="n">
+      <c r="I18" s="11">
         <v>135</v>
       </c>
       <c r="J18" s="9"/>
@@ -1243,14 +1220,14 @@
       <c r="O18" s="9"/>
       <c r="P18" s="8"/>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B19" s="13" t="n">
+    <row r="19" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="13">
         <v>46243</v>
       </c>
       <c r="C19" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="D19" s="14" t="n">
+      <c r="D19" s="14">
         <v>2</v>
       </c>
       <c r="E19" s="14" t="s">
@@ -1263,7 +1240,7 @@
       <c r="H19" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="I19" s="14" t="n">
+      <c r="I19" s="14">
         <v>0</v>
       </c>
       <c r="J19" s="9"/>
@@ -1274,14 +1251,14 @@
       <c r="O19" s="9"/>
       <c r="P19" s="8"/>
     </row>
-    <row r="20" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="13" t="n">
+    <row r="20" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="13">
         <v>46244</v>
       </c>
       <c r="C20" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="D20" s="14" t="n">
+      <c r="D20" s="14">
         <v>3</v>
       </c>
       <c r="E20" s="14" t="s">
@@ -1294,7 +1271,7 @@
       <c r="H20" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="I20" s="14" t="n">
+      <c r="I20" s="14">
         <v>0</v>
       </c>
       <c r="J20" s="9"/>
@@ -1305,14 +1282,14 @@
       <c r="O20" s="9"/>
       <c r="P20" s="8"/>
     </row>
-    <row r="21" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B21" s="5" t="n">
+    <row r="21" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="5">
         <v>46245</v>
       </c>
       <c r="C21" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D21" s="6" t="n">
+      <c r="D21" s="6">
         <v>3</v>
       </c>
       <c r="E21" s="6" t="s">
@@ -1325,7 +1302,7 @@
       <c r="H21" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="I21" s="6" t="n">
+      <c r="I21" s="6">
         <v>65</v>
       </c>
       <c r="J21" s="9"/>
@@ -1336,14 +1313,14 @@
       <c r="O21" s="9"/>
       <c r="P21" s="8"/>
     </row>
-    <row r="22" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B22" s="10" t="n">
+    <row r="22" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="10">
         <v>46246</v>
       </c>
       <c r="C22" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="D22" s="11" t="n">
+      <c r="D22" s="11">
         <v>3</v>
       </c>
       <c r="E22" s="11" t="s">
@@ -1356,7 +1333,7 @@
       <c r="H22" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="I22" s="11" t="n">
+      <c r="I22" s="11">
         <v>55</v>
       </c>
       <c r="J22" s="9"/>
@@ -1367,14 +1344,14 @@
       <c r="O22" s="9"/>
       <c r="P22" s="8"/>
     </row>
-    <row r="23" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B23" s="13" t="n">
+    <row r="23" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="13">
         <v>46247</v>
       </c>
       <c r="C23" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="D23" s="14" t="n">
+      <c r="D23" s="14">
         <v>3</v>
       </c>
       <c r="E23" s="14" t="s">
@@ -1387,7 +1364,7 @@
       <c r="H23" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="I23" s="14" t="n">
+      <c r="I23" s="14">
         <v>0</v>
       </c>
       <c r="J23" s="9"/>
@@ -1398,14 +1375,14 @@
       <c r="O23" s="9"/>
       <c r="P23" s="8"/>
     </row>
-    <row r="24" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="5" t="n">
+    <row r="24" spans="2:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="5">
         <v>46248</v>
       </c>
       <c r="C24" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D24" s="6" t="n">
+      <c r="D24" s="6">
         <v>3</v>
       </c>
       <c r="E24" s="6" t="s">
@@ -1418,7 +1395,7 @@
       <c r="H24" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="I24" s="6" t="n">
+      <c r="I24" s="6">
         <v>50</v>
       </c>
       <c r="J24" s="9"/>
@@ -1429,14 +1406,14 @@
       <c r="O24" s="9"/>
       <c r="P24" s="8"/>
     </row>
-    <row r="25" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B25" s="10" t="n">
+    <row r="25" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B25" s="10">
         <v>46249</v>
       </c>
       <c r="C25" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="D25" s="11" t="n">
+      <c r="D25" s="11">
         <v>3</v>
       </c>
       <c r="E25" s="11" t="s">
@@ -1449,7 +1426,7 @@
       <c r="H25" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="I25" s="11" t="n">
+      <c r="I25" s="11">
         <v>140</v>
       </c>
       <c r="J25" s="9"/>
@@ -1460,14 +1437,14 @@
       <c r="O25" s="9"/>
       <c r="P25" s="8"/>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B26" s="13" t="n">
+    <row r="26" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="13">
         <v>46250</v>
       </c>
       <c r="C26" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="D26" s="14" t="n">
+      <c r="D26" s="14">
         <v>3</v>
       </c>
       <c r="E26" s="14" t="s">
@@ -1480,7 +1457,7 @@
       <c r="H26" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="I26" s="14" t="n">
+      <c r="I26" s="14">
         <v>0</v>
       </c>
       <c r="J26" s="9"/>
@@ -1491,14 +1468,14 @@
       <c r="O26" s="9"/>
       <c r="P26" s="8"/>
     </row>
-    <row r="27" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B27" s="13" t="n">
+    <row r="27" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B27" s="13">
         <v>46251</v>
       </c>
       <c r="C27" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="D27" s="14" t="n">
+      <c r="D27" s="14">
         <v>4</v>
       </c>
       <c r="E27" s="14" t="s">
@@ -1511,7 +1488,7 @@
       <c r="H27" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="I27" s="14" t="n">
+      <c r="I27" s="14">
         <v>0</v>
       </c>
       <c r="J27" s="9"/>
@@ -1522,14 +1499,14 @@
       <c r="O27" s="9"/>
       <c r="P27" s="8"/>
     </row>
-    <row r="28" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B28" s="5" t="n">
+    <row r="28" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="5">
         <v>46252</v>
       </c>
       <c r="C28" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D28" s="6" t="n">
+      <c r="D28" s="6">
         <v>4</v>
       </c>
       <c r="E28" s="6" t="s">
@@ -1542,7 +1519,7 @@
       <c r="H28" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="I28" s="6" t="n">
+      <c r="I28" s="6">
         <v>65</v>
       </c>
       <c r="J28" s="9"/>
@@ -1553,14 +1530,14 @@
       <c r="O28" s="9"/>
       <c r="P28" s="8"/>
     </row>
-    <row r="29" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B29" s="10" t="n">
+    <row r="29" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B29" s="10">
         <v>46253</v>
       </c>
       <c r="C29" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="D29" s="11" t="n">
+      <c r="D29" s="11">
         <v>4</v>
       </c>
       <c r="E29" s="11" t="s">
@@ -1573,7 +1550,7 @@
       <c r="H29" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="I29" s="11" t="n">
+      <c r="I29" s="11">
         <v>57</v>
       </c>
       <c r="J29" s="9"/>
@@ -1584,14 +1561,14 @@
       <c r="O29" s="9"/>
       <c r="P29" s="8"/>
     </row>
-    <row r="30" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B30" s="13" t="n">
+    <row r="30" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B30" s="13">
         <v>46254</v>
       </c>
       <c r="C30" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="D30" s="14" t="n">
+      <c r="D30" s="14">
         <v>4</v>
       </c>
       <c r="E30" s="14" t="s">
@@ -1604,7 +1581,7 @@
       <c r="H30" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="I30" s="14" t="n">
+      <c r="I30" s="14">
         <v>0</v>
       </c>
       <c r="J30" s="9"/>
@@ -1615,14 +1592,14 @@
       <c r="O30" s="9"/>
       <c r="P30" s="8"/>
     </row>
-    <row r="31" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B31" s="5" t="n">
+    <row r="31" spans="2:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B31" s="5">
         <v>46255</v>
       </c>
       <c r="C31" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D31" s="6" t="n">
+      <c r="D31" s="6">
         <v>4</v>
       </c>
       <c r="E31" s="6" t="s">
@@ -1635,7 +1612,7 @@
       <c r="H31" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="I31" s="6" t="n">
+      <c r="I31" s="6">
         <v>50</v>
       </c>
       <c r="J31" s="9"/>
@@ -1646,14 +1623,14 @@
       <c r="O31" s="9"/>
       <c r="P31" s="8"/>
     </row>
-    <row r="32" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B32" s="10" t="n">
+    <row r="32" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="10">
         <v>46256</v>
       </c>
       <c r="C32" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="D32" s="11" t="n">
+      <c r="D32" s="11">
         <v>4</v>
       </c>
       <c r="E32" s="11" t="s">
@@ -1666,7 +1643,7 @@
       <c r="H32" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="I32" s="11" t="n">
+      <c r="I32" s="11">
         <v>140</v>
       </c>
       <c r="J32" s="9"/>
@@ -1677,14 +1654,14 @@
       <c r="O32" s="9"/>
       <c r="P32" s="8"/>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B33" s="13" t="n">
+    <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B33" s="13">
         <v>46257</v>
       </c>
       <c r="C33" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="D33" s="14" t="n">
+      <c r="D33" s="14">
         <v>4</v>
       </c>
       <c r="E33" s="14" t="s">
@@ -1697,7 +1674,7 @@
       <c r="H33" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="I33" s="14" t="n">
+      <c r="I33" s="14">
         <v>0</v>
       </c>
       <c r="J33" s="9"/>
@@ -1708,14 +1685,14 @@
       <c r="O33" s="9"/>
       <c r="P33" s="8"/>
     </row>
-    <row r="34" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B34" s="13" t="n">
+    <row r="34" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B34" s="13">
         <v>46258</v>
       </c>
       <c r="C34" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="D34" s="14" t="n">
+      <c r="D34" s="14">
         <v>5</v>
       </c>
       <c r="E34" s="14" t="s">
@@ -1728,7 +1705,7 @@
       <c r="H34" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="I34" s="14" t="n">
+      <c r="I34" s="14">
         <v>0</v>
       </c>
       <c r="J34" s="9"/>
@@ -1739,14 +1716,14 @@
       <c r="O34" s="9"/>
       <c r="P34" s="8"/>
     </row>
-    <row r="35" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B35" s="5" t="n">
+    <row r="35" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B35" s="5">
         <v>46259</v>
       </c>
       <c r="C35" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D35" s="6" t="n">
+      <c r="D35" s="6">
         <v>5</v>
       </c>
       <c r="E35" s="6" t="s">
@@ -1759,7 +1736,7 @@
       <c r="H35" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="I35" s="6" t="n">
+      <c r="I35" s="6">
         <v>65</v>
       </c>
       <c r="J35" s="9"/>
@@ -1770,14 +1747,14 @@
       <c r="O35" s="9"/>
       <c r="P35" s="8"/>
     </row>
-    <row r="36" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B36" s="10" t="n">
+    <row r="36" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="10">
         <v>46260</v>
       </c>
       <c r="C36" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="D36" s="11" t="n">
+      <c r="D36" s="11">
         <v>5</v>
       </c>
       <c r="E36" s="11" t="s">
@@ -1790,7 +1767,7 @@
       <c r="H36" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="I36" s="11" t="n">
+      <c r="I36" s="11">
         <v>58</v>
       </c>
       <c r="J36" s="9"/>
@@ -1801,14 +1778,14 @@
       <c r="O36" s="9"/>
       <c r="P36" s="8"/>
     </row>
-    <row r="37" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B37" s="13" t="n">
+    <row r="37" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B37" s="13">
         <v>46261</v>
       </c>
       <c r="C37" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="D37" s="14" t="n">
+      <c r="D37" s="14">
         <v>5</v>
       </c>
       <c r="E37" s="14" t="s">
@@ -1821,7 +1798,7 @@
       <c r="H37" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="I37" s="14" t="n">
+      <c r="I37" s="14">
         <v>0</v>
       </c>
       <c r="J37" s="9"/>
@@ -1832,14 +1809,14 @@
       <c r="O37" s="9"/>
       <c r="P37" s="8"/>
     </row>
-    <row r="38" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="5" t="n">
+    <row r="38" spans="2:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B38" s="5">
         <v>46262</v>
       </c>
       <c r="C38" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D38" s="6" t="n">
+      <c r="D38" s="6">
         <v>5</v>
       </c>
       <c r="E38" s="6" t="s">
@@ -1852,7 +1829,7 @@
       <c r="H38" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="I38" s="6" t="n">
+      <c r="I38" s="6">
         <v>50</v>
       </c>
       <c r="J38" s="9"/>
@@ -1863,14 +1840,14 @@
       <c r="O38" s="9"/>
       <c r="P38" s="8"/>
     </row>
-    <row r="39" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B39" s="10" t="n">
+    <row r="39" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B39" s="10">
         <v>46263</v>
       </c>
       <c r="C39" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="D39" s="11" t="n">
+      <c r="D39" s="11">
         <v>5</v>
       </c>
       <c r="E39" s="11" t="s">
@@ -1883,7 +1860,7 @@
       <c r="H39" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="I39" s="11" t="n">
+      <c r="I39" s="11">
         <v>145</v>
       </c>
       <c r="J39" s="9"/>
@@ -1894,14 +1871,14 @@
       <c r="O39" s="9"/>
       <c r="P39" s="8"/>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B40" s="13" t="n">
+    <row r="40" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B40" s="13">
         <v>46264</v>
       </c>
       <c r="C40" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="D40" s="14" t="n">
+      <c r="D40" s="14">
         <v>5</v>
       </c>
       <c r="E40" s="14" t="s">
@@ -1914,7 +1891,7 @@
       <c r="H40" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="I40" s="14" t="n">
+      <c r="I40" s="14">
         <v>0</v>
       </c>
       <c r="J40" s="9"/>
@@ -1925,14 +1902,14 @@
       <c r="O40" s="9"/>
       <c r="P40" s="8"/>
     </row>
-    <row r="41" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B41" s="13" t="n">
+    <row r="41" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B41" s="13">
         <v>46265</v>
       </c>
       <c r="C41" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="D41" s="14" t="n">
+      <c r="D41" s="14">
         <v>6</v>
       </c>
       <c r="E41" s="14" t="s">
@@ -1945,7 +1922,7 @@
       <c r="H41" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="I41" s="14" t="n">
+      <c r="I41" s="14">
         <v>0</v>
       </c>
       <c r="J41" s="9"/>
@@ -1956,14 +1933,14 @@
       <c r="O41" s="9"/>
       <c r="P41" s="8"/>
     </row>
-    <row r="42" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B42" s="5" t="n">
+    <row r="42" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B42" s="5">
         <v>46266</v>
       </c>
       <c r="C42" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D42" s="6" t="n">
+      <c r="D42" s="6">
         <v>6</v>
       </c>
       <c r="E42" s="6" t="s">
@@ -1976,7 +1953,7 @@
       <c r="H42" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="I42" s="6" t="n">
+      <c r="I42" s="6">
         <v>65</v>
       </c>
       <c r="J42" s="9"/>
@@ -1987,14 +1964,14 @@
       <c r="O42" s="9"/>
       <c r="P42" s="8"/>
     </row>
-    <row r="43" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B43" s="10" t="n">
+    <row r="43" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B43" s="10">
         <v>46267</v>
       </c>
       <c r="C43" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="D43" s="11" t="n">
+      <c r="D43" s="11">
         <v>6</v>
       </c>
       <c r="E43" s="11" t="s">
@@ -2007,7 +1984,7 @@
       <c r="H43" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="I43" s="11" t="n">
+      <c r="I43" s="11">
         <v>59</v>
       </c>
       <c r="J43" s="9"/>
@@ -2018,14 +1995,14 @@
       <c r="O43" s="9"/>
       <c r="P43" s="8"/>
     </row>
-    <row r="44" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B44" s="13" t="n">
+    <row r="44" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B44" s="13">
         <v>46268</v>
       </c>
       <c r="C44" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="D44" s="14" t="n">
+      <c r="D44" s="14">
         <v>6</v>
       </c>
       <c r="E44" s="14" t="s">
@@ -2038,7 +2015,7 @@
       <c r="H44" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="I44" s="14" t="n">
+      <c r="I44" s="14">
         <v>0</v>
       </c>
       <c r="J44" s="9"/>
@@ -2049,14 +2026,14 @@
       <c r="O44" s="9"/>
       <c r="P44" s="8"/>
     </row>
-    <row r="45" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B45" s="5" t="n">
+    <row r="45" spans="2:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B45" s="5">
         <v>46269</v>
       </c>
       <c r="C45" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D45" s="6" t="n">
+      <c r="D45" s="6">
         <v>6</v>
       </c>
       <c r="E45" s="6" t="s">
@@ -2069,7 +2046,7 @@
       <c r="H45" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="I45" s="6" t="n">
+      <c r="I45" s="6">
         <v>50</v>
       </c>
       <c r="J45" s="9"/>
@@ -2080,14 +2057,14 @@
       <c r="O45" s="9"/>
       <c r="P45" s="8"/>
     </row>
-    <row r="46" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B46" s="10" t="n">
+    <row r="46" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B46" s="10">
         <v>46270</v>
       </c>
       <c r="C46" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="D46" s="11" t="n">
+      <c r="D46" s="11">
         <v>6</v>
       </c>
       <c r="E46" s="11" t="s">
@@ -2100,7 +2077,7 @@
       <c r="H46" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="I46" s="11" t="n">
+      <c r="I46" s="11">
         <v>145</v>
       </c>
       <c r="J46" s="9"/>
@@ -2111,14 +2088,14 @@
       <c r="O46" s="9"/>
       <c r="P46" s="8"/>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B47" s="13" t="n">
+    <row r="47" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B47" s="13">
         <v>46271</v>
       </c>
       <c r="C47" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="D47" s="14" t="n">
+      <c r="D47" s="14">
         <v>6</v>
       </c>
       <c r="E47" s="14" t="s">
@@ -2131,7 +2108,7 @@
       <c r="H47" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="I47" s="14" t="n">
+      <c r="I47" s="14">
         <v>0</v>
       </c>
       <c r="J47" s="9"/>
@@ -2142,14 +2119,14 @@
       <c r="O47" s="9"/>
       <c r="P47" s="8"/>
     </row>
-    <row r="48" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B48" s="13" t="n">
+    <row r="48" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B48" s="13">
         <v>46272</v>
       </c>
       <c r="C48" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="D48" s="14" t="n">
+      <c r="D48" s="14">
         <v>7</v>
       </c>
       <c r="E48" s="14" t="s">
@@ -2162,7 +2139,7 @@
       <c r="H48" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="I48" s="14" t="n">
+      <c r="I48" s="14">
         <v>0</v>
       </c>
       <c r="J48" s="9"/>
@@ -2173,14 +2150,14 @@
       <c r="O48" s="9"/>
       <c r="P48" s="8"/>
     </row>
-    <row r="49" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B49" s="5" t="n">
+    <row r="49" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B49" s="5">
         <v>46273</v>
       </c>
       <c r="C49" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D49" s="6" t="n">
+      <c r="D49" s="6">
         <v>7</v>
       </c>
       <c r="E49" s="6" t="s">
@@ -2193,7 +2170,7 @@
       <c r="H49" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="I49" s="6" t="n">
+      <c r="I49" s="6">
         <v>65</v>
       </c>
       <c r="J49" s="9"/>
@@ -2204,14 +2181,14 @@
       <c r="O49" s="9"/>
       <c r="P49" s="8"/>
     </row>
-    <row r="50" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B50" s="10" t="n">
+    <row r="50" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B50" s="10">
         <v>46274</v>
       </c>
       <c r="C50" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="D50" s="11" t="n">
+      <c r="D50" s="11">
         <v>7</v>
       </c>
       <c r="E50" s="11" t="s">
@@ -2224,7 +2201,7 @@
       <c r="H50" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="I50" s="11" t="n">
+      <c r="I50" s="11">
         <v>60</v>
       </c>
       <c r="J50" s="9"/>
@@ -2235,14 +2212,14 @@
       <c r="O50" s="9"/>
       <c r="P50" s="8"/>
     </row>
-    <row r="51" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B51" s="13" t="n">
+    <row r="51" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B51" s="13">
         <v>46275</v>
       </c>
       <c r="C51" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="D51" s="14" t="n">
+      <c r="D51" s="14">
         <v>7</v>
       </c>
       <c r="E51" s="14" t="s">
@@ -2255,7 +2232,7 @@
       <c r="H51" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="I51" s="14" t="n">
+      <c r="I51" s="14">
         <v>0</v>
       </c>
       <c r="J51" s="9"/>
@@ -2266,14 +2243,14 @@
       <c r="O51" s="9"/>
       <c r="P51" s="8"/>
     </row>
-    <row r="52" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B52" s="5" t="n">
+    <row r="52" spans="2:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B52" s="5">
         <v>46276</v>
       </c>
       <c r="C52" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D52" s="6" t="n">
+      <c r="D52" s="6">
         <v>7</v>
       </c>
       <c r="E52" s="6" t="s">
@@ -2286,7 +2263,7 @@
       <c r="H52" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="I52" s="6" t="n">
+      <c r="I52" s="6">
         <v>50</v>
       </c>
       <c r="J52" s="9"/>
@@ -2297,14 +2274,14 @@
       <c r="O52" s="9"/>
       <c r="P52" s="8"/>
     </row>
-    <row r="53" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B53" s="10" t="n">
+    <row r="53" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B53" s="10">
         <v>46277</v>
       </c>
       <c r="C53" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="D53" s="11" t="n">
+      <c r="D53" s="11">
         <v>7</v>
       </c>
       <c r="E53" s="11" t="s">
@@ -2317,7 +2294,7 @@
       <c r="H53" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="I53" s="11" t="n">
+      <c r="I53" s="11">
         <v>145</v>
       </c>
       <c r="J53" s="9"/>
@@ -2328,14 +2305,14 @@
       <c r="O53" s="9"/>
       <c r="P53" s="8"/>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B54" s="13" t="n">
+    <row r="54" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B54" s="13">
         <v>46278</v>
       </c>
       <c r="C54" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="D54" s="14" t="n">
+      <c r="D54" s="14">
         <v>7</v>
       </c>
       <c r="E54" s="14" t="s">
@@ -2348,7 +2325,7 @@
       <c r="H54" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="I54" s="14" t="n">
+      <c r="I54" s="14">
         <v>0</v>
       </c>
       <c r="J54" s="9"/>
@@ -2359,14 +2336,14 @@
       <c r="O54" s="9"/>
       <c r="P54" s="8"/>
     </row>
-    <row r="55" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B55" s="13" t="n">
+    <row r="55" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B55" s="13">
         <v>46279</v>
       </c>
       <c r="C55" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="D55" s="14" t="n">
+      <c r="D55" s="14">
         <v>8</v>
       </c>
       <c r="E55" s="14" t="s">
@@ -2379,7 +2356,7 @@
       <c r="H55" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="I55" s="14" t="n">
+      <c r="I55" s="14">
         <v>0</v>
       </c>
       <c r="J55" s="9"/>
@@ -2390,14 +2367,14 @@
       <c r="O55" s="9"/>
       <c r="P55" s="8"/>
     </row>
-    <row r="56" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B56" s="5" t="n">
+    <row r="56" spans="2:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B56" s="5">
         <v>46280</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="D56" s="6" t="n">
+      <c r="D56" s="6">
         <v>8</v>
       </c>
       <c r="E56" s="6" t="s">
@@ -2410,7 +2387,7 @@
       <c r="H56" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="I56" s="6" t="n">
+      <c r="I56" s="6">
         <v>65</v>
       </c>
       <c r="J56" s="9"/>
@@ -2421,14 +2398,14 @@
       <c r="O56" s="9"/>
       <c r="P56" s="8"/>
     </row>
-    <row r="57" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B57" s="10" t="n">
+    <row r="57" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B57" s="10">
         <v>46281</v>
       </c>
       <c r="C57" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="D57" s="11" t="n">
+      <c r="D57" s="11">
         <v>8</v>
       </c>
       <c r="E57" s="11" t="s">
@@ -2441,7 +2418,7 @@
       <c r="H57" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="I57" s="11" t="n">
+      <c r="I57" s="11">
         <v>60</v>
       </c>
       <c r="J57" s="9"/>
@@ -2452,14 +2429,14 @@
       <c r="O57" s="9"/>
       <c r="P57" s="8"/>
     </row>
-    <row r="58" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B58" s="13" t="n">
+    <row r="58" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B58" s="13">
         <v>46282</v>
       </c>
       <c r="C58" s="14" t="s">
         <v>31</v>
       </c>
-      <c r="D58" s="14" t="n">
+      <c r="D58" s="14">
         <v>8</v>
       </c>
       <c r="E58" s="14" t="s">
@@ -2472,7 +2449,7 @@
       <c r="H58" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="I58" s="14" t="n">
+      <c r="I58" s="14">
         <v>0</v>
       </c>
       <c r="J58" s="9"/>
@@ -2483,14 +2460,14 @@
       <c r="O58" s="9"/>
       <c r="P58" s="8"/>
     </row>
-    <row r="59" customFormat="false" ht="34.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B59" s="5" t="n">
+    <row r="59" spans="2:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B59" s="5">
         <v>46283</v>
       </c>
       <c r="C59" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="D59" s="6" t="n">
+      <c r="D59" s="6">
         <v>8</v>
       </c>
       <c r="E59" s="6" t="s">
@@ -2503,7 +2480,7 @@
       <c r="H59" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="I59" s="6" t="n">
+      <c r="I59" s="6">
         <v>50</v>
       </c>
       <c r="J59" s="9"/>
@@ -2514,14 +2491,14 @@
       <c r="O59" s="9"/>
       <c r="P59" s="8"/>
     </row>
-    <row r="60" customFormat="false" ht="23.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B60" s="10" t="n">
+    <row r="60" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B60" s="10">
         <v>46284</v>
       </c>
       <c r="C60" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="D60" s="11" t="n">
+      <c r="D60" s="11">
         <v>8</v>
       </c>
       <c r="E60" s="11" t="s">
@@ -2534,7 +2511,7 @@
       <c r="H60" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="I60" s="11" t="n">
+      <c r="I60" s="11">
         <v>145</v>
       </c>
       <c r="J60" s="9"/>
@@ -2545,14 +2522,14 @@
       <c r="O60" s="9"/>
       <c r="P60" s="8"/>
     </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B61" s="13" t="n">
+    <row r="61" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B61" s="13">
         <v>46285</v>
       </c>
       <c r="C61" s="14" t="s">
         <v>39</v>
       </c>
-      <c r="D61" s="14" t="n">
+      <c r="D61" s="14">
         <v>8</v>
       </c>
       <c r="E61" s="14" t="s">
@@ -2565,7 +2542,7 @@
       <c r="H61" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="I61" s="14" t="n">
+      <c r="I61" s="14">
         <v>0</v>
       </c>
       <c r="J61" s="9"/>
@@ -2578,46 +2555,38 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="H6:H61" type="list">
+    <dataValidation type="list" allowBlank="1" sqref="H6:H61" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"Planned,Done,Modified,Skipped"</formula1>
       <formula2>0</formula2>
     </dataValidation>
   </dataValidations>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B2:F14"/>
-  <sheetFormatPr defaultColWidth="8.71484375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="4" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="10"/>
+    <col min="2" max="2" width="8" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="5" width="20" customWidth="1"/>
+    <col min="6" max="6" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="16" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
         <v>5</v>
       </c>
@@ -2634,225 +2603,217 @@
         <v>57</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B6" s="17" t="n">
+    <row r="6" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="17">
         <v>1</v>
       </c>
-      <c r="C6" s="17" t="n">
-        <f aca="false">COUNTIFS(Log!$D$6:$D$61,B6,Log!$H$6:$H$61,"Done")</f>
-        <v>1</v>
-      </c>
-      <c r="D6" s="17" t="n">
-        <f aca="false">SUMIFS(Log!$J$6:$J$61,Log!$D$6:$D$61,B6)</f>
-        <v>65</v>
-      </c>
-      <c r="E6" s="17" t="n">
-        <f aca="false">SUMIFS(Log!$K$6:$K$61,Log!$D$6:$D$61,B6)</f>
-        <v>5.01</v>
-      </c>
-      <c r="F6" s="17" t="n">
-        <f aca="false">IFERROR(AVERAGEIFS(Log!$O$6:$O$61,Log!$D$6:$D$61,B6,Log!$H$6:$H$61,"Done"),"")</f>
+      <c r="C6" s="17">
+        <f>COUNTIFS(Log!$D$6:$D$61,B6,Log!$H$6:$H$61,"Done")</f>
+        <v>2</v>
+      </c>
+      <c r="D6" s="17">
+        <f>SUMIFS(Log!$J$6:$J$61,Log!$D$6:$D$61,B6)</f>
+        <v>120</v>
+      </c>
+      <c r="E6" s="17">
+        <f>SUMIFS(Log!$K$6:$K$61,Log!$D$6:$D$61,B6)</f>
+        <v>7.81</v>
+      </c>
+      <c r="F6" s="17">
+        <f>IFERROR(AVERAGEIFS(Log!$O$6:$O$61,Log!$D$6:$D$61,B6,Log!$H$6:$H$61,"Done"),"")</f>
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="17">
+        <v>2</v>
+      </c>
+      <c r="C7" s="17">
+        <f>COUNTIFS(Log!$D$6:$D$61,B7,Log!$H$6:$H$61,"Done")</f>
+        <v>0</v>
+      </c>
+      <c r="D7" s="17">
+        <f>SUMIFS(Log!$J$6:$J$61,Log!$D$6:$D$61,B7)</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="17">
+        <f>SUMIFS(Log!$K$6:$K$61,Log!$D$6:$D$61,B7)</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="17" t="str">
+        <f>IFERROR(AVERAGEIFS(Log!$O$6:$O$61,Log!$D$6:$D$61,B7,Log!$H$6:$H$61,"Done"),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="17">
+        <v>3</v>
+      </c>
+      <c r="C8" s="17">
+        <f>COUNTIFS(Log!$D$6:$D$61,B8,Log!$H$6:$H$61,"Done")</f>
+        <v>0</v>
+      </c>
+      <c r="D8" s="17">
+        <f>SUMIFS(Log!$J$6:$J$61,Log!$D$6:$D$61,B8)</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="17">
+        <f>SUMIFS(Log!$K$6:$K$61,Log!$D$6:$D$61,B8)</f>
+        <v>0</v>
+      </c>
+      <c r="F8" s="17" t="str">
+        <f>IFERROR(AVERAGEIFS(Log!$O$6:$O$61,Log!$D$6:$D$61,B8,Log!$H$6:$H$61,"Done"),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="17">
+        <v>4</v>
+      </c>
+      <c r="C9" s="17">
+        <f>COUNTIFS(Log!$D$6:$D$61,B9,Log!$H$6:$H$61,"Done")</f>
+        <v>0</v>
+      </c>
+      <c r="D9" s="17">
+        <f>SUMIFS(Log!$J$6:$J$61,Log!$D$6:$D$61,B9)</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="17">
+        <f>SUMIFS(Log!$K$6:$K$61,Log!$D$6:$D$61,B9)</f>
+        <v>0</v>
+      </c>
+      <c r="F9" s="17" t="str">
+        <f>IFERROR(AVERAGEIFS(Log!$O$6:$O$61,Log!$D$6:$D$61,B9,Log!$H$6:$H$61,"Done"),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="17">
         <v>5</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B7" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="C7" s="17" t="n">
-        <f aca="false">COUNTIFS(Log!$D$6:$D$61,B7,Log!$H$6:$H$61,"Done")</f>
-        <v>0</v>
-      </c>
-      <c r="D7" s="17" t="n">
-        <f aca="false">SUMIFS(Log!$J$6:$J$61,Log!$D$6:$D$61,B7)</f>
-        <v>0</v>
-      </c>
-      <c r="E7" s="17" t="n">
-        <f aca="false">SUMIFS(Log!$K$6:$K$61,Log!$D$6:$D$61,B7)</f>
-        <v>0</v>
-      </c>
-      <c r="F7" s="17" t="str">
-        <f aca="false">IFERROR(AVERAGEIFS(Log!$O$6:$O$61,Log!$D$6:$D$61,B7,Log!$H$6:$H$61,"Done"),"")</f>
+      <c r="C10" s="17">
+        <f>COUNTIFS(Log!$D$6:$D$61,B10,Log!$H$6:$H$61,"Done")</f>
+        <v>0</v>
+      </c>
+      <c r="D10" s="17">
+        <f>SUMIFS(Log!$J$6:$J$61,Log!$D$6:$D$61,B10)</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="17">
+        <f>SUMIFS(Log!$K$6:$K$61,Log!$D$6:$D$61,B10)</f>
+        <v>0</v>
+      </c>
+      <c r="F10" s="17" t="str">
+        <f>IFERROR(AVERAGEIFS(Log!$O$6:$O$61,Log!$D$6:$D$61,B10,Log!$H$6:$H$61,"Done"),"")</f>
         <v/>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B8" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="C8" s="17" t="n">
-        <f aca="false">COUNTIFS(Log!$D$6:$D$61,B8,Log!$H$6:$H$61,"Done")</f>
-        <v>0</v>
-      </c>
-      <c r="D8" s="17" t="n">
-        <f aca="false">SUMIFS(Log!$J$6:$J$61,Log!$D$6:$D$61,B8)</f>
-        <v>0</v>
-      </c>
-      <c r="E8" s="17" t="n">
-        <f aca="false">SUMIFS(Log!$K$6:$K$61,Log!$D$6:$D$61,B8)</f>
-        <v>0</v>
-      </c>
-      <c r="F8" s="17" t="str">
-        <f aca="false">IFERROR(AVERAGEIFS(Log!$O$6:$O$61,Log!$D$6:$D$61,B8,Log!$H$6:$H$61,"Done"),"")</f>
+    <row r="11" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="17">
+        <v>6</v>
+      </c>
+      <c r="C11" s="17">
+        <f>COUNTIFS(Log!$D$6:$D$61,B11,Log!$H$6:$H$61,"Done")</f>
+        <v>0</v>
+      </c>
+      <c r="D11" s="17">
+        <f>SUMIFS(Log!$J$6:$J$61,Log!$D$6:$D$61,B11)</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="17">
+        <f>SUMIFS(Log!$K$6:$K$61,Log!$D$6:$D$61,B11)</f>
+        <v>0</v>
+      </c>
+      <c r="F11" s="17" t="str">
+        <f>IFERROR(AVERAGEIFS(Log!$O$6:$O$61,Log!$D$6:$D$61,B11,Log!$H$6:$H$61,"Done"),"")</f>
         <v/>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B9" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="C9" s="17" t="n">
-        <f aca="false">COUNTIFS(Log!$D$6:$D$61,B9,Log!$H$6:$H$61,"Done")</f>
-        <v>0</v>
-      </c>
-      <c r="D9" s="17" t="n">
-        <f aca="false">SUMIFS(Log!$J$6:$J$61,Log!$D$6:$D$61,B9)</f>
-        <v>0</v>
-      </c>
-      <c r="E9" s="17" t="n">
-        <f aca="false">SUMIFS(Log!$K$6:$K$61,Log!$D$6:$D$61,B9)</f>
-        <v>0</v>
-      </c>
-      <c r="F9" s="17" t="str">
-        <f aca="false">IFERROR(AVERAGEIFS(Log!$O$6:$O$61,Log!$D$6:$D$61,B9,Log!$H$6:$H$61,"Done"),"")</f>
+    <row r="12" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="17">
+        <v>7</v>
+      </c>
+      <c r="C12" s="17">
+        <f>COUNTIFS(Log!$D$6:$D$61,B12,Log!$H$6:$H$61,"Done")</f>
+        <v>0</v>
+      </c>
+      <c r="D12" s="17">
+        <f>SUMIFS(Log!$J$6:$J$61,Log!$D$6:$D$61,B12)</f>
+        <v>0</v>
+      </c>
+      <c r="E12" s="17">
+        <f>SUMIFS(Log!$K$6:$K$61,Log!$D$6:$D$61,B12)</f>
+        <v>0</v>
+      </c>
+      <c r="F12" s="17" t="str">
+        <f>IFERROR(AVERAGEIFS(Log!$O$6:$O$61,Log!$D$6:$D$61,B12,Log!$H$6:$H$61,"Done"),"")</f>
         <v/>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B10" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="C10" s="17" t="n">
-        <f aca="false">COUNTIFS(Log!$D$6:$D$61,B10,Log!$H$6:$H$61,"Done")</f>
-        <v>0</v>
-      </c>
-      <c r="D10" s="17" t="n">
-        <f aca="false">SUMIFS(Log!$J$6:$J$61,Log!$D$6:$D$61,B10)</f>
-        <v>0</v>
-      </c>
-      <c r="E10" s="17" t="n">
-        <f aca="false">SUMIFS(Log!$K$6:$K$61,Log!$D$6:$D$61,B10)</f>
-        <v>0</v>
-      </c>
-      <c r="F10" s="17" t="str">
-        <f aca="false">IFERROR(AVERAGEIFS(Log!$O$6:$O$61,Log!$D$6:$D$61,B10,Log!$H$6:$H$61,"Done"),"")</f>
+    <row r="13" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="17">
+        <v>8</v>
+      </c>
+      <c r="C13" s="17">
+        <f>COUNTIFS(Log!$D$6:$D$61,B13,Log!$H$6:$H$61,"Done")</f>
+        <v>0</v>
+      </c>
+      <c r="D13" s="17">
+        <f>SUMIFS(Log!$J$6:$J$61,Log!$D$6:$D$61,B13)</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="17">
+        <f>SUMIFS(Log!$K$6:$K$61,Log!$D$6:$D$61,B13)</f>
+        <v>0</v>
+      </c>
+      <c r="F13" s="17" t="str">
+        <f>IFERROR(AVERAGEIFS(Log!$O$6:$O$61,Log!$D$6:$D$61,B13,Log!$H$6:$H$61,"Done"),"")</f>
         <v/>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B11" s="17" t="n">
-        <v>6</v>
-      </c>
-      <c r="C11" s="17" t="n">
-        <f aca="false">COUNTIFS(Log!$D$6:$D$61,B11,Log!$H$6:$H$61,"Done")</f>
-        <v>0</v>
-      </c>
-      <c r="D11" s="17" t="n">
-        <f aca="false">SUMIFS(Log!$J$6:$J$61,Log!$D$6:$D$61,B11)</f>
-        <v>0</v>
-      </c>
-      <c r="E11" s="17" t="n">
-        <f aca="false">SUMIFS(Log!$K$6:$K$61,Log!$D$6:$D$61,B11)</f>
-        <v>0</v>
-      </c>
-      <c r="F11" s="17" t="str">
-        <f aca="false">IFERROR(AVERAGEIFS(Log!$O$6:$O$61,Log!$D$6:$D$61,B11,Log!$H$6:$H$61,"Done"),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B12" s="17" t="n">
-        <v>7</v>
-      </c>
-      <c r="C12" s="17" t="n">
-        <f aca="false">COUNTIFS(Log!$D$6:$D$61,B12,Log!$H$6:$H$61,"Done")</f>
-        <v>0</v>
-      </c>
-      <c r="D12" s="17" t="n">
-        <f aca="false">SUMIFS(Log!$J$6:$J$61,Log!$D$6:$D$61,B12)</f>
-        <v>0</v>
-      </c>
-      <c r="E12" s="17" t="n">
-        <f aca="false">SUMIFS(Log!$K$6:$K$61,Log!$D$6:$D$61,B12)</f>
-        <v>0</v>
-      </c>
-      <c r="F12" s="17" t="str">
-        <f aca="false">IFERROR(AVERAGEIFS(Log!$O$6:$O$61,Log!$D$6:$D$61,B12,Log!$H$6:$H$61,"Done"),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B13" s="17" t="n">
-        <v>8</v>
-      </c>
-      <c r="C13" s="17" t="n">
-        <f aca="false">COUNTIFS(Log!$D$6:$D$61,B13,Log!$H$6:$H$61,"Done")</f>
-        <v>0</v>
-      </c>
-      <c r="D13" s="17" t="n">
-        <f aca="false">SUMIFS(Log!$J$6:$J$61,Log!$D$6:$D$61,B13)</f>
-        <v>0</v>
-      </c>
-      <c r="E13" s="17" t="n">
-        <f aca="false">SUMIFS(Log!$K$6:$K$61,Log!$D$6:$D$61,B13)</f>
-        <v>0</v>
-      </c>
-      <c r="F13" s="17" t="str">
-        <f aca="false">IFERROR(AVERAGEIFS(Log!$O$6:$O$61,Log!$D$6:$D$61,B13,Log!$H$6:$H$61,"Done"),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="14" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="C14" s="19" t="n">
-        <f aca="false">SUM(C6:C13)</f>
-        <v>1</v>
-      </c>
-      <c r="D14" s="19" t="n">
-        <f aca="false">SUM(D6:D13)</f>
-        <v>65</v>
-      </c>
-      <c r="E14" s="19" t="n">
-        <f aca="false">SUM(E6:E13)</f>
-        <v>5.01</v>
+      <c r="C14" s="19">
+        <f>SUM(C6:C13)</f>
+        <v>2</v>
+      </c>
+      <c r="D14" s="19">
+        <f>SUM(D6:D13)</f>
+        <v>120</v>
+      </c>
+      <c r="E14" s="19">
+        <f>SUM(E6:E13)</f>
+        <v>7.81</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B2:C17"/>
-  <sheetFormatPr defaultColWidth="8.71484375" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="95"/>
+    <col min="2" max="2" width="26" customWidth="1"/>
+    <col min="3" max="3" width="95" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" spans="2:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="16" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" spans="2:3" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="20" t="s">
         <v>61</v>
       </c>
@@ -2860,7 +2821,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" spans="2:3" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="20" t="s">
         <v>63</v>
       </c>
@@ -2868,7 +2829,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" spans="2:3" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="20" t="s">
         <v>65</v>
       </c>
@@ -2876,7 +2837,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="70.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" spans="2:3" ht="70.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="20" t="s">
         <v>67</v>
       </c>
@@ -2884,7 +2845,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="77.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="13" spans="2:3" ht="77.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="20" t="s">
         <v>69</v>
       </c>
@@ -2892,7 +2853,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="15" spans="2:3" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="20" t="s">
         <v>71</v>
       </c>
@@ -2900,7 +2861,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="45.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="17" spans="2:3" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="20" t="s">
         <v>73</v>
       </c>
@@ -2909,12 +2870,7 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
--- a/Marathon_Training_Log.xlsx
+++ b/Marathon_Training_Log.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Coursework\24-Git_Projects\02-Marathon_Training_Personal\Marathon_Training\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E872A67B-7BA3-4853-A146-5E5F12D5872C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B89335B4-9C4E-4387-8E03-527676C3C1EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="79">
   <si>
     <t>Marathon Training Log — Pre-Super Base</t>
   </si>
@@ -274,6 +274,12 @@
 First 10 min warmup + last remaining cooldown walk.
 Heart rate was jumping. But maintained conversational pace in between. Cooldown/recovery saw a heartrate drop of around 10-15 bpm from the Max.
 Used treadmill.</t>
+  </si>
+  <si>
+    <t>30 min Strength for Runners with Andy Speer</t>
+  </si>
+  <si>
+    <t>Strength training for runners. Used 15 lb dumbell pair. Not overloading.</t>
   </si>
 </sst>
 </file>
@@ -895,20 +901,36 @@
       <c r="F8" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="G8" s="8"/>
+      <c r="G8" s="8" t="s">
+        <v>77</v>
+      </c>
       <c r="H8" s="9" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="I8" s="14">
         <v>0</v>
       </c>
-      <c r="J8" s="9"/>
-      <c r="K8" s="9"/>
-      <c r="L8" s="9"/>
-      <c r="M8" s="9"/>
-      <c r="N8" s="9"/>
-      <c r="O8" s="9"/>
-      <c r="P8" s="8"/>
+      <c r="J8" s="9">
+        <v>30</v>
+      </c>
+      <c r="K8" s="9">
+        <v>0</v>
+      </c>
+      <c r="L8" s="9">
+        <v>0</v>
+      </c>
+      <c r="M8" s="9">
+        <v>108</v>
+      </c>
+      <c r="N8" s="9">
+        <v>146</v>
+      </c>
+      <c r="O8" s="9">
+        <v>4</v>
+      </c>
+      <c r="P8" s="8" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="9" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="5">
@@ -2609,11 +2631,11 @@
       </c>
       <c r="C6" s="17">
         <f>COUNTIFS(Log!$D$6:$D$61,B6,Log!$H$6:$H$61,"Done")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D6" s="17">
         <f>SUMIFS(Log!$J$6:$J$61,Log!$D$6:$D$61,B6)</f>
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="E6" s="17">
         <f>SUMIFS(Log!$K$6:$K$61,Log!$D$6:$D$61,B6)</f>
@@ -2621,7 +2643,7 @@
       </c>
       <c r="F6" s="17">
         <f>IFERROR(AVERAGEIFS(Log!$O$6:$O$61,Log!$D$6:$D$61,B6,Log!$H$6:$H$61,"Done"),"")</f>
-        <v>5.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2777,11 +2799,11 @@
       </c>
       <c r="C14" s="19">
         <f>SUM(C6:C13)</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D14" s="19">
         <f>SUM(D6:D13)</f>
-        <v>120</v>
+        <v>150</v>
       </c>
       <c r="E14" s="19">
         <f>SUM(E6:E13)</f>

--- a/Marathon_Training_Log.xlsx
+++ b/Marathon_Training_Log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Coursework\24-Git_Projects\02-Marathon_Training_Personal\Marathon_Training\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B89335B4-9C4E-4387-8E03-527676C3C1EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59B5974C-51BC-4176-8EE9-B79A92B493FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="81">
   <si>
     <t>Marathon Training Log — Pre-Super Base</t>
   </si>
@@ -280,6 +280,12 @@
   </si>
   <si>
     <t>Strength training for runners. Used 15 lb dumbell pair. Not overloading.</t>
+  </si>
+  <si>
+    <t>30 min Pop Run with Selena Samuela + Apple Run for 15 min</t>
+  </si>
+  <si>
+    <t>Easy run. Did some minor pushes inadvertently. Still felt good with nose breathing for most part. Last 15 min walked more due to incline.</t>
   </si>
 </sst>
 </file>
@@ -870,7 +876,7 @@
         <v>2.8</v>
       </c>
       <c r="L7" s="9">
-        <v>3.7</v>
+        <v>16.2</v>
       </c>
       <c r="M7" s="9">
         <v>144</v>
@@ -948,20 +954,36 @@
       <c r="F9" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="G9" s="8"/>
+      <c r="G9" s="8" t="s">
+        <v>79</v>
+      </c>
       <c r="H9" s="9" t="s">
         <v>27</v>
       </c>
       <c r="I9" s="6">
         <v>50</v>
       </c>
-      <c r="J9" s="9"/>
-      <c r="K9" s="9"/>
-      <c r="L9" s="9"/>
-      <c r="M9" s="9"/>
-      <c r="N9" s="9"/>
-      <c r="O9" s="9"/>
-      <c r="P9" s="8"/>
+      <c r="J9" s="9">
+        <v>50</v>
+      </c>
+      <c r="K9" s="9">
+        <v>3.43</v>
+      </c>
+      <c r="L9" s="9">
+        <v>13.11</v>
+      </c>
+      <c r="M9" s="9">
+        <v>140</v>
+      </c>
+      <c r="N9" s="9">
+        <v>188</v>
+      </c>
+      <c r="O9" s="9">
+        <v>5</v>
+      </c>
+      <c r="P9" s="8" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="10" spans="2:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="10">
@@ -2635,11 +2657,11 @@
       </c>
       <c r="D6" s="17">
         <f>SUMIFS(Log!$J$6:$J$61,Log!$D$6:$D$61,B6)</f>
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="E6" s="17">
         <f>SUMIFS(Log!$K$6:$K$61,Log!$D$6:$D$61,B6)</f>
-        <v>7.81</v>
+        <v>11.24</v>
       </c>
       <c r="F6" s="17">
         <f>IFERROR(AVERAGEIFS(Log!$O$6:$O$61,Log!$D$6:$D$61,B6,Log!$H$6:$H$61,"Done"),"")</f>
@@ -2803,11 +2825,11 @@
       </c>
       <c r="D14" s="19">
         <f>SUM(D6:D13)</f>
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="E14" s="19">
         <f>SUM(E6:E13)</f>
-        <v>7.81</v>
+        <v>11.24</v>
       </c>
     </row>
   </sheetData>

--- a/Marathon_Training_Log.xlsx
+++ b/Marathon_Training_Log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Coursework\24-Git_Projects\02-Marathon_Training_Personal\Marathon_Training\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{59B5974C-51BC-4176-8EE9-B79A92B493FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B44FC740-BF5F-49F8-87A1-B835DE252064}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="274" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="83">
   <si>
     <t>Marathon Training Log — Pre-Super Base</t>
   </si>
@@ -286,6 +286,12 @@
   </si>
   <si>
     <t>Easy run. Did some minor pushes inadvertently. Still felt good with nose breathing for most part. Last 15 min walked more due to incline.</t>
+  </si>
+  <si>
+    <t>20 min Advanced Beginner Run with Olivia Amato + 20 min total Apple workout + cooldown + stretching</t>
+  </si>
+  <si>
+    <t>Coupled easy run as warmup then performed the drills for Hill Blast.</t>
   </si>
 </sst>
 </file>
@@ -1001,20 +1007,36 @@
       <c r="F10" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="G10" s="8"/>
+      <c r="G10" s="8" t="s">
+        <v>81</v>
+      </c>
       <c r="H10" s="9" t="s">
         <v>27</v>
       </c>
       <c r="I10" s="11">
         <v>45</v>
       </c>
-      <c r="J10" s="9"/>
-      <c r="K10" s="9"/>
-      <c r="L10" s="9"/>
-      <c r="M10" s="9"/>
-      <c r="N10" s="9"/>
-      <c r="O10" s="9"/>
-      <c r="P10" s="8"/>
+      <c r="J10" s="9">
+        <v>45</v>
+      </c>
+      <c r="K10" s="9">
+        <v>2.4700000000000002</v>
+      </c>
+      <c r="L10" s="9">
+        <v>15.23</v>
+      </c>
+      <c r="M10" s="9">
+        <v>134</v>
+      </c>
+      <c r="N10" s="9">
+        <v>161</v>
+      </c>
+      <c r="O10" s="9">
+        <v>4</v>
+      </c>
+      <c r="P10" s="8" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="11" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="10">
@@ -2657,11 +2679,11 @@
       </c>
       <c r="D6" s="17">
         <f>SUMIFS(Log!$J$6:$J$61,Log!$D$6:$D$61,B6)</f>
-        <v>200</v>
+        <v>245</v>
       </c>
       <c r="E6" s="17">
         <f>SUMIFS(Log!$K$6:$K$61,Log!$D$6:$D$61,B6)</f>
-        <v>11.24</v>
+        <v>13.71</v>
       </c>
       <c r="F6" s="17">
         <f>IFERROR(AVERAGEIFS(Log!$O$6:$O$61,Log!$D$6:$D$61,B6,Log!$H$6:$H$61,"Done"),"")</f>
@@ -2825,11 +2847,11 @@
       </c>
       <c r="D14" s="19">
         <f>SUM(D6:D13)</f>
-        <v>200</v>
+        <v>245</v>
       </c>
       <c r="E14" s="19">
         <f>SUM(E6:E13)</f>
-        <v>11.24</v>
+        <v>13.71</v>
       </c>
     </row>
   </sheetData>

--- a/Marathon_Training_Log.xlsx
+++ b/Marathon_Training_Log.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Coursework\24-Git_Projects\02-Marathon_Training_Personal\Marathon_Training\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B44FC740-BF5F-49F8-87A1-B835DE252064}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1190F2A4-D578-4511-845D-27334B2C88D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Log" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="88">
   <si>
     <t>Marathon Training Log — Pre-Super Base</t>
   </si>
@@ -292,6 +292,21 @@
   </si>
   <si>
     <t>Coupled easy run as warmup then performed the drills for Hill Blast.</t>
+  </si>
+  <si>
+    <t>Tracked via Apple Watch + 10 min warmup class</t>
+  </si>
+  <si>
+    <t>Easy run. Heart rate still climed up, but the occasional walks helped heart rate to come down. Forgot headphones that did cause some unease.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Walk </t>
+  </si>
+  <si>
+    <t>Long walk with the dog to move around. No exersion at all.</t>
+  </si>
+  <si>
+    <t>Plan to finish the Strength class from week 1</t>
   </si>
 </sst>
 </file>
@@ -1054,20 +1069,36 @@
       <c r="F11" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="G11" s="8"/>
+      <c r="G11" s="8" t="s">
+        <v>83</v>
+      </c>
       <c r="H11" s="9" t="s">
         <v>27</v>
       </c>
       <c r="I11" s="11">
         <v>90</v>
       </c>
-      <c r="J11" s="9"/>
-      <c r="K11" s="9"/>
-      <c r="L11" s="9"/>
-      <c r="M11" s="9"/>
-      <c r="N11" s="9"/>
-      <c r="O11" s="9"/>
-      <c r="P11" s="8"/>
+      <c r="J11" s="9">
+        <v>90</v>
+      </c>
+      <c r="K11" s="9">
+        <v>7.18</v>
+      </c>
+      <c r="L11" s="9">
+        <v>12.3</v>
+      </c>
+      <c r="M11" s="9">
+        <v>160</v>
+      </c>
+      <c r="N11" s="9">
+        <v>178</v>
+      </c>
+      <c r="O11" s="9">
+        <v>5</v>
+      </c>
+      <c r="P11" s="8" t="s">
+        <v>84</v>
+      </c>
     </row>
     <row r="12" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="13">
@@ -1085,20 +1116,36 @@
       <c r="F12" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="G12" s="8"/>
+      <c r="G12" s="8" t="s">
+        <v>85</v>
+      </c>
       <c r="H12" s="9" t="s">
         <v>27</v>
       </c>
       <c r="I12" s="14">
         <v>0</v>
       </c>
-      <c r="J12" s="9"/>
-      <c r="K12" s="9"/>
-      <c r="L12" s="9"/>
-      <c r="M12" s="9"/>
-      <c r="N12" s="9"/>
-      <c r="O12" s="9"/>
-      <c r="P12" s="8"/>
+      <c r="J12" s="9">
+        <v>45</v>
+      </c>
+      <c r="K12" s="9">
+        <v>1.76</v>
+      </c>
+      <c r="L12" s="9">
+        <v>26.49</v>
+      </c>
+      <c r="M12" s="9">
+        <v>97</v>
+      </c>
+      <c r="N12" s="9">
+        <v>106</v>
+      </c>
+      <c r="O12" s="9">
+        <v>2</v>
+      </c>
+      <c r="P12" s="8" t="s">
+        <v>86</v>
+      </c>
     </row>
     <row r="13" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="13">
@@ -1116,7 +1163,9 @@
       <c r="F13" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="G13" s="8"/>
+      <c r="G13" s="8" t="s">
+        <v>87</v>
+      </c>
       <c r="H13" s="9" t="s">
         <v>27</v>
       </c>
@@ -2679,11 +2728,11 @@
       </c>
       <c r="D6" s="17">
         <f>SUMIFS(Log!$J$6:$J$61,Log!$D$6:$D$61,B6)</f>
-        <v>245</v>
+        <v>380</v>
       </c>
       <c r="E6" s="17">
         <f>SUMIFS(Log!$K$6:$K$61,Log!$D$6:$D$61,B6)</f>
-        <v>13.71</v>
+        <v>22.650000000000002</v>
       </c>
       <c r="F6" s="17">
         <f>IFERROR(AVERAGEIFS(Log!$O$6:$O$61,Log!$D$6:$D$61,B6,Log!$H$6:$H$61,"Done"),"")</f>
@@ -2847,11 +2896,11 @@
       </c>
       <c r="D14" s="19">
         <f>SUM(D6:D13)</f>
-        <v>245</v>
+        <v>380</v>
       </c>
       <c r="E14" s="19">
         <f>SUM(E6:E13)</f>
-        <v>13.71</v>
+        <v>22.650000000000002</v>
       </c>
     </row>
   </sheetData>

--- a/Marathon_Training_Log.xlsx
+++ b/Marathon_Training_Log.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Coursework\24-Git_Projects\02-Marathon_Training_Personal\Marathon_Training\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\04-Personal\01-Marathon Training\Marathon_Training\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1190F2A4-D578-4511-845D-27334B2C88D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1C18ED4-6FAD-4139-A6BE-7C5C9872E42A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Log" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="284" uniqueCount="91">
   <si>
     <t>Marathon Training Log — Pre-Super Base</t>
   </si>
@@ -307,6 +307,15 @@
   </si>
   <si>
     <t>Plan to finish the Strength class from week 1</t>
+  </si>
+  <si>
+    <t>Strength training for runners. Used 22.5 lb dumbell pair. Not overloading. Took it easy where necessary.</t>
+  </si>
+  <si>
+    <t>10 min Pre-Run Warm Up with Matt Wilpers + 45 min Tempo Run with Becs Gentry + Evening Run 20 min</t>
+  </si>
+  <si>
+    <t>Predominantly nose breathing. Easy run. Heart rate was still slightly higher with hilly portions on the route. Exploring new routes.</t>
   </si>
 </sst>
 </file>
@@ -1172,13 +1181,27 @@
       <c r="I13" s="14">
         <v>0</v>
       </c>
-      <c r="J13" s="9"/>
-      <c r="K13" s="9"/>
-      <c r="L13" s="9"/>
-      <c r="M13" s="9"/>
-      <c r="N13" s="9"/>
-      <c r="O13" s="9"/>
-      <c r="P13" s="8"/>
+      <c r="J13" s="9">
+        <v>30</v>
+      </c>
+      <c r="K13" s="9">
+        <v>0</v>
+      </c>
+      <c r="L13" s="9">
+        <v>0</v>
+      </c>
+      <c r="M13" s="9">
+        <v>120</v>
+      </c>
+      <c r="N13" s="9">
+        <v>155</v>
+      </c>
+      <c r="O13" s="9">
+        <v>4</v>
+      </c>
+      <c r="P13" s="8" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="14" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="5">
@@ -1196,20 +1219,36 @@
       <c r="F14" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="8"/>
+      <c r="G14" s="8" t="s">
+        <v>89</v>
+      </c>
       <c r="H14" s="9" t="s">
         <v>27</v>
       </c>
       <c r="I14" s="6">
         <v>65</v>
       </c>
-      <c r="J14" s="9"/>
-      <c r="K14" s="9"/>
-      <c r="L14" s="9"/>
-      <c r="M14" s="9"/>
-      <c r="N14" s="9"/>
-      <c r="O14" s="9"/>
-      <c r="P14" s="8"/>
+      <c r="J14" s="9">
+        <v>65</v>
+      </c>
+      <c r="K14" s="9">
+        <v>4.87</v>
+      </c>
+      <c r="L14" s="9">
+        <v>13.34</v>
+      </c>
+      <c r="M14" s="9">
+        <v>154</v>
+      </c>
+      <c r="N14" s="9">
+        <v>165</v>
+      </c>
+      <c r="O14" s="9">
+        <v>5</v>
+      </c>
+      <c r="P14" s="8" t="s">
+        <v>90</v>
+      </c>
     </row>
     <row r="15" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="10">
@@ -2749,11 +2788,11 @@
       </c>
       <c r="D7" s="17">
         <f>SUMIFS(Log!$J$6:$J$61,Log!$D$6:$D$61,B7)</f>
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="E7" s="17">
         <f>SUMIFS(Log!$K$6:$K$61,Log!$D$6:$D$61,B7)</f>
-        <v>0</v>
+        <v>4.87</v>
       </c>
       <c r="F7" s="17" t="str">
         <f>IFERROR(AVERAGEIFS(Log!$O$6:$O$61,Log!$D$6:$D$61,B7,Log!$H$6:$H$61,"Done"),"")</f>
@@ -2896,11 +2935,11 @@
       </c>
       <c r="D14" s="19">
         <f>SUM(D6:D13)</f>
-        <v>380</v>
+        <v>475</v>
       </c>
       <c r="E14" s="19">
         <f>SUM(E6:E13)</f>
-        <v>22.650000000000002</v>
+        <v>27.520000000000003</v>
       </c>
     </row>
   </sheetData>

--- a/Marathon_Training_Log.xlsx
+++ b/Marathon_Training_Log.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Coursework\24-Git_Projects\02-Marathon_Training_Personal\Marathon_Training\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1190F2A4-D578-4511-845D-27334B2C88D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96B86BE2-D554-4372-A969-92E023529C9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="500" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Log" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="102">
   <si>
     <t>Marathon Training Log — Pre-Super Base</t>
   </si>
@@ -306,7 +306,49 @@
     <t>Long walk with the dog to move around. No exersion at all.</t>
   </si>
   <si>
-    <t>Plan to finish the Strength class from week 1</t>
+    <t>Combination of 45 min Tempo Run with Becs Gentry + 10 min Pre-Run Warm Up with Matt Wilpers + 10 min cooldown</t>
+  </si>
+  <si>
+    <t>Actual run excluding WU and CD to be 45 matchign class. Distance 3.79 miles. Running behind by 1 day.</t>
+  </si>
+  <si>
+    <t>Did striders on Saturday bur un on 10AUG2026 Monday</t>
+  </si>
+  <si>
+    <t>Did long run this day.</t>
+  </si>
+  <si>
+    <t>30 min 2010s Run with Adrian Williams + 20 min run</t>
+  </si>
+  <si>
+    <t>45 min Marathon Race Prep with Robin Arzon + 10 min Pre run warmup</t>
+  </si>
+  <si>
+    <t>45 min Tempo Run with Becs Gentry  + 20 min run</t>
+  </si>
+  <si>
+    <t>30 min Strength for funners with Rebecca Kennedy</t>
+  </si>
+  <si>
+    <t>Strength training</t>
+  </si>
+  <si>
+    <t>Nose breathing run</t>
+  </si>
+  <si>
+    <t>Night walk</t>
+  </si>
+  <si>
+    <t>Just walk</t>
+  </si>
+  <si>
+    <t>Rested</t>
+  </si>
+  <si>
+    <t>Saturdays long run done this day. Too much hilly route. Definitely had to slow down.</t>
+  </si>
+  <si>
+    <t>Just did striders.</t>
   </si>
 </sst>
 </file>
@@ -1164,7 +1206,7 @@
         <v>30</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="H13" s="9" t="s">
         <v>27</v>
@@ -1172,13 +1214,27 @@
       <c r="I13" s="14">
         <v>0</v>
       </c>
-      <c r="J13" s="9"/>
-      <c r="K13" s="9"/>
-      <c r="L13" s="9"/>
-      <c r="M13" s="9"/>
-      <c r="N13" s="9"/>
-      <c r="O13" s="9"/>
-      <c r="P13" s="8"/>
+      <c r="J13" s="9">
+        <v>30</v>
+      </c>
+      <c r="K13" s="9">
+        <v>0</v>
+      </c>
+      <c r="L13" s="9">
+        <v>0</v>
+      </c>
+      <c r="M13" s="9">
+        <v>120</v>
+      </c>
+      <c r="N13" s="9">
+        <v>155</v>
+      </c>
+      <c r="O13" s="9">
+        <v>3</v>
+      </c>
+      <c r="P13" s="8" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="14" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="5">
@@ -1196,20 +1252,36 @@
       <c r="F14" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="8"/>
+      <c r="G14" s="8" t="s">
+        <v>93</v>
+      </c>
       <c r="H14" s="9" t="s">
         <v>27</v>
       </c>
       <c r="I14" s="6">
         <v>65</v>
       </c>
-      <c r="J14" s="9"/>
-      <c r="K14" s="9"/>
-      <c r="L14" s="9"/>
-      <c r="M14" s="9"/>
-      <c r="N14" s="9"/>
-      <c r="O14" s="9"/>
-      <c r="P14" s="8"/>
+      <c r="J14" s="9">
+        <v>65</v>
+      </c>
+      <c r="K14" s="9">
+        <v>4.87</v>
+      </c>
+      <c r="L14" s="9">
+        <v>12.55</v>
+      </c>
+      <c r="M14" s="9">
+        <v>153</v>
+      </c>
+      <c r="N14" s="9">
+        <v>165</v>
+      </c>
+      <c r="O14" s="9">
+        <v>5</v>
+      </c>
+      <c r="P14" s="8" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="15" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="10">
@@ -1227,20 +1299,36 @@
       <c r="F15" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="G15" s="8"/>
+      <c r="G15" s="8" t="s">
+        <v>92</v>
+      </c>
       <c r="H15" s="9" t="s">
         <v>27</v>
       </c>
       <c r="I15" s="11">
         <v>52</v>
       </c>
-      <c r="J15" s="9"/>
-      <c r="K15" s="9"/>
-      <c r="L15" s="9"/>
-      <c r="M15" s="9"/>
-      <c r="N15" s="9"/>
-      <c r="O15" s="9"/>
-      <c r="P15" s="8"/>
+      <c r="J15" s="9">
+        <v>55</v>
+      </c>
+      <c r="K15" s="9">
+        <v>3.73</v>
+      </c>
+      <c r="L15" s="9">
+        <v>12.45</v>
+      </c>
+      <c r="M15" s="9">
+        <v>155</v>
+      </c>
+      <c r="N15" s="9">
+        <v>178</v>
+      </c>
+      <c r="O15" s="9">
+        <v>5</v>
+      </c>
+      <c r="P15" s="8" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="16" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="13">
@@ -1258,20 +1346,34 @@
       <c r="F16" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="G16" s="8"/>
+      <c r="G16" s="8" t="s">
+        <v>97</v>
+      </c>
       <c r="H16" s="9" t="s">
         <v>27</v>
       </c>
       <c r="I16" s="14">
         <v>0</v>
       </c>
-      <c r="J16" s="9"/>
-      <c r="K16" s="9"/>
+      <c r="J16" s="9">
+        <v>22</v>
+      </c>
+      <c r="K16" s="9">
+        <v>0.86</v>
+      </c>
       <c r="L16" s="9"/>
-      <c r="M16" s="9"/>
-      <c r="N16" s="9"/>
-      <c r="O16" s="9"/>
-      <c r="P16" s="8"/>
+      <c r="M16" s="9">
+        <v>104</v>
+      </c>
+      <c r="N16" s="9">
+        <v>123</v>
+      </c>
+      <c r="O16" s="9">
+        <v>2</v>
+      </c>
+      <c r="P16" s="8" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="17" spans="2:16" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="5">
@@ -1289,19 +1391,33 @@
       <c r="F17" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="G17" s="8"/>
+      <c r="G17" s="8" t="s">
+        <v>91</v>
+      </c>
       <c r="H17" s="9" t="s">
         <v>27</v>
       </c>
       <c r="I17" s="6">
         <v>50</v>
       </c>
-      <c r="J17" s="9"/>
-      <c r="K17" s="9"/>
-      <c r="L17" s="9"/>
-      <c r="M17" s="9"/>
-      <c r="N17" s="9"/>
-      <c r="O17" s="9"/>
+      <c r="J17" s="9">
+        <v>50</v>
+      </c>
+      <c r="K17" s="9">
+        <v>3.74</v>
+      </c>
+      <c r="L17" s="9">
+        <v>13.02</v>
+      </c>
+      <c r="M17" s="9">
+        <v>146</v>
+      </c>
+      <c r="N17" s="9">
+        <v>165</v>
+      </c>
+      <c r="O17" s="9">
+        <v>5</v>
+      </c>
       <c r="P17" s="8"/>
     </row>
     <row r="18" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1320,20 +1436,36 @@
       <c r="F18" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="G18" s="8"/>
+      <c r="G18" s="8" t="s">
+        <v>89</v>
+      </c>
       <c r="H18" s="9" t="s">
         <v>27</v>
       </c>
       <c r="I18" s="11">
         <v>135</v>
       </c>
-      <c r="J18" s="9"/>
-      <c r="K18" s="9"/>
-      <c r="L18" s="9"/>
-      <c r="M18" s="9"/>
-      <c r="N18" s="9"/>
-      <c r="O18" s="9"/>
-      <c r="P18" s="8"/>
+      <c r="J18" s="9">
+        <v>20</v>
+      </c>
+      <c r="K18" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="L18" s="9">
+        <v>14.13</v>
+      </c>
+      <c r="M18" s="9">
+        <v>145</v>
+      </c>
+      <c r="N18" s="9">
+        <v>162</v>
+      </c>
+      <c r="O18" s="9">
+        <v>5</v>
+      </c>
+      <c r="P18" s="8" t="s">
+        <v>101</v>
+      </c>
     </row>
     <row r="19" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="13">
@@ -1351,19 +1483,33 @@
       <c r="F19" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="G19" s="8"/>
+      <c r="G19" s="8" t="s">
+        <v>99</v>
+      </c>
       <c r="H19" s="9" t="s">
         <v>27</v>
       </c>
       <c r="I19" s="14">
         <v>0</v>
       </c>
-      <c r="J19" s="9"/>
-      <c r="K19" s="9"/>
-      <c r="L19" s="9"/>
-      <c r="M19" s="9"/>
-      <c r="N19" s="9"/>
-      <c r="O19" s="9"/>
+      <c r="J19" s="9">
+        <v>0</v>
+      </c>
+      <c r="K19" s="9">
+        <v>0</v>
+      </c>
+      <c r="L19" s="9">
+        <v>0</v>
+      </c>
+      <c r="M19" s="9">
+        <v>0</v>
+      </c>
+      <c r="N19" s="9">
+        <v>0</v>
+      </c>
+      <c r="O19" s="9">
+        <v>0</v>
+      </c>
       <c r="P19" s="8"/>
     </row>
     <row r="20" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1382,20 +1528,36 @@
       <c r="F20" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="G20" s="8"/>
+      <c r="G20" s="8" t="s">
+        <v>90</v>
+      </c>
       <c r="H20" s="9" t="s">
         <v>27</v>
       </c>
       <c r="I20" s="14">
         <v>0</v>
       </c>
-      <c r="J20" s="9"/>
-      <c r="K20" s="9"/>
-      <c r="L20" s="9"/>
-      <c r="M20" s="9"/>
-      <c r="N20" s="9"/>
-      <c r="O20" s="9"/>
-      <c r="P20" s="8"/>
+      <c r="J20" s="9">
+        <v>135</v>
+      </c>
+      <c r="K20" s="9">
+        <v>5.73</v>
+      </c>
+      <c r="L20" s="9">
+        <v>14.13</v>
+      </c>
+      <c r="M20" s="9">
+        <v>145</v>
+      </c>
+      <c r="N20" s="9">
+        <v>162</v>
+      </c>
+      <c r="O20" s="9">
+        <v>5</v>
+      </c>
+      <c r="P20" s="8" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="21" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="5">
@@ -1413,20 +1575,36 @@
       <c r="F21" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G21" s="8"/>
+      <c r="G21" s="8" t="s">
+        <v>87</v>
+      </c>
       <c r="H21" s="9" t="s">
         <v>27</v>
       </c>
       <c r="I21" s="6">
         <v>65</v>
       </c>
-      <c r="J21" s="9"/>
-      <c r="K21" s="9"/>
-      <c r="L21" s="9"/>
-      <c r="M21" s="9"/>
-      <c r="N21" s="9"/>
-      <c r="O21" s="9"/>
-      <c r="P21" s="8"/>
+      <c r="J21" s="9">
+        <v>65</v>
+      </c>
+      <c r="K21" s="9">
+        <v>4.5</v>
+      </c>
+      <c r="L21" s="9">
+        <v>11.52</v>
+      </c>
+      <c r="M21" s="9">
+        <v>156</v>
+      </c>
+      <c r="N21" s="9">
+        <v>169</v>
+      </c>
+      <c r="O21" s="9">
+        <v>5</v>
+      </c>
+      <c r="P21" s="8" t="s">
+        <v>88</v>
+      </c>
     </row>
     <row r="22" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="10">
@@ -2749,11 +2927,11 @@
       </c>
       <c r="D7" s="17">
         <f>SUMIFS(Log!$J$6:$J$61,Log!$D$6:$D$61,B7)</f>
-        <v>0</v>
+        <v>242</v>
       </c>
       <c r="E7" s="17">
         <f>SUMIFS(Log!$K$6:$K$61,Log!$D$6:$D$61,B7)</f>
-        <v>0</v>
+        <v>13.7</v>
       </c>
       <c r="F7" s="17" t="str">
         <f>IFERROR(AVERAGEIFS(Log!$O$6:$O$61,Log!$D$6:$D$61,B7,Log!$H$6:$H$61,"Done"),"")</f>
@@ -2770,11 +2948,11 @@
       </c>
       <c r="D8" s="17">
         <f>SUMIFS(Log!$J$6:$J$61,Log!$D$6:$D$61,B8)</f>
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="E8" s="17">
         <f>SUMIFS(Log!$K$6:$K$61,Log!$D$6:$D$61,B8)</f>
-        <v>0</v>
+        <v>10.23</v>
       </c>
       <c r="F8" s="17" t="str">
         <f>IFERROR(AVERAGEIFS(Log!$O$6:$O$61,Log!$D$6:$D$61,B8,Log!$H$6:$H$61,"Done"),"")</f>
@@ -2896,11 +3074,11 @@
       </c>
       <c r="D14" s="19">
         <f>SUM(D6:D13)</f>
-        <v>380</v>
+        <v>822</v>
       </c>
       <c r="E14" s="19">
         <f>SUM(E6:E13)</f>
-        <v>22.650000000000002</v>
+        <v>46.58</v>
       </c>
     </row>
   </sheetData>

--- a/Marathon_Training_Log.xlsx
+++ b/Marathon_Training_Log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Coursework\24-Git_Projects\02-Marathon_Training_Personal\Marathon_Training\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96B86BE2-D554-4372-A969-92E023529C9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{040620A6-2116-4C2E-B71F-336EC0B2C5CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="568" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="106">
   <si>
     <t>Marathon Training Log — Pre-Super Base</t>
   </si>
@@ -348,7 +348,19 @@
     <t>Saturdays long run done this day. Too much hilly route. Definitely had to slow down.</t>
   </si>
   <si>
-    <t>Just did striders.</t>
+    <t>Modified</t>
+  </si>
+  <si>
+    <t>Just did striders. Actual long run done on 10AUG2026 Monday.</t>
+  </si>
+  <si>
+    <t>10 min Pre-Run Warm Up with Becs Gentry + 34 min Marathon Race Prep with Matt Wilpers + Night Run</t>
+  </si>
+  <si>
+    <t>Did the internval training as recommended. Skipped last 2 min add on. This run was actually done on Thrusday. Friday's rest was utilized here.</t>
+  </si>
+  <si>
+    <t>Did Wednesday's run here.</t>
   </si>
 </sst>
 </file>
@@ -1021,7 +1033,7 @@
         <v>79</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="I9" s="6">
         <v>50</v>
@@ -1068,7 +1080,7 @@
         <v>81</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="I10" s="11">
         <v>45</v>
@@ -1115,7 +1127,7 @@
         <v>83</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="I11" s="11">
         <v>90</v>
@@ -1162,7 +1174,7 @@
         <v>85</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>27</v>
+        <v>101</v>
       </c>
       <c r="I12" s="14">
         <v>0</v>
@@ -1209,7 +1221,7 @@
         <v>94</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>27</v>
+        <v>101</v>
       </c>
       <c r="I13" s="14">
         <v>0</v>
@@ -1256,7 +1268,7 @@
         <v>93</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="I14" s="6">
         <v>65</v>
@@ -1303,7 +1315,7 @@
         <v>92</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="I15" s="11">
         <v>52</v>
@@ -1350,7 +1362,7 @@
         <v>97</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>27</v>
+        <v>101</v>
       </c>
       <c r="I16" s="14">
         <v>0</v>
@@ -1395,7 +1407,7 @@
         <v>91</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="I17" s="6">
         <v>50</v>
@@ -1440,7 +1452,7 @@
         <v>89</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>27</v>
+        <v>101</v>
       </c>
       <c r="I18" s="11">
         <v>135</v>
@@ -1464,7 +1476,7 @@
         <v>5</v>
       </c>
       <c r="P18" s="8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="19" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1487,7 +1499,7 @@
         <v>99</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="I19" s="14">
         <v>0</v>
@@ -1532,7 +1544,7 @@
         <v>90</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="I20" s="14">
         <v>0</v>
@@ -1579,7 +1591,7 @@
         <v>87</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="I21" s="6">
         <v>65</v>
@@ -1622,20 +1634,36 @@
       <c r="F22" s="12" t="s">
         <v>44</v>
       </c>
-      <c r="G22" s="8"/>
+      <c r="G22" s="8" t="s">
+        <v>103</v>
+      </c>
       <c r="H22" s="9" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="I22" s="11">
         <v>55</v>
       </c>
-      <c r="J22" s="9"/>
-      <c r="K22" s="9"/>
-      <c r="L22" s="9"/>
-      <c r="M22" s="9"/>
-      <c r="N22" s="9"/>
-      <c r="O22" s="9"/>
-      <c r="P22" s="8"/>
+      <c r="J22" s="9">
+        <v>70</v>
+      </c>
+      <c r="K22" s="9">
+        <v>4.18</v>
+      </c>
+      <c r="L22" s="9">
+        <v>14.12</v>
+      </c>
+      <c r="M22" s="9">
+        <v>149</v>
+      </c>
+      <c r="N22" s="9">
+        <v>176</v>
+      </c>
+      <c r="O22" s="9">
+        <v>7</v>
+      </c>
+      <c r="P22" s="8" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="23" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="13">
@@ -1655,7 +1683,7 @@
       </c>
       <c r="G23" s="8"/>
       <c r="H23" s="9" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="I23" s="14">
         <v>0</v>
@@ -1666,7 +1694,9 @@
       <c r="M23" s="9"/>
       <c r="N23" s="9"/>
       <c r="O23" s="9"/>
-      <c r="P23" s="8"/>
+      <c r="P23" s="8" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="24" spans="2:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="5">
@@ -2902,7 +2932,7 @@
       </c>
       <c r="C6" s="17">
         <f>COUNTIFS(Log!$D$6:$D$61,B6,Log!$H$6:$H$61,"Done")</f>
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D6" s="17">
         <f>SUMIFS(Log!$J$6:$J$61,Log!$D$6:$D$61,B6)</f>
@@ -2914,7 +2944,7 @@
       </c>
       <c r="F6" s="17">
         <f>IFERROR(AVERAGEIFS(Log!$O$6:$O$61,Log!$D$6:$D$61,B6,Log!$H$6:$H$61,"Done"),"")</f>
-        <v>5</v>
+        <v>4.833333333333333</v>
       </c>
     </row>
     <row r="7" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2923,7 +2953,7 @@
       </c>
       <c r="C7" s="17">
         <f>COUNTIFS(Log!$D$6:$D$61,B7,Log!$H$6:$H$61,"Done")</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D7" s="17">
         <f>SUMIFS(Log!$J$6:$J$61,Log!$D$6:$D$61,B7)</f>
@@ -2933,9 +2963,9 @@
         <f>SUMIFS(Log!$K$6:$K$61,Log!$D$6:$D$61,B7)</f>
         <v>13.7</v>
       </c>
-      <c r="F7" s="17" t="str">
+      <c r="F7" s="17">
         <f>IFERROR(AVERAGEIFS(Log!$O$6:$O$61,Log!$D$6:$D$61,B7,Log!$H$6:$H$61,"Done"),"")</f>
-        <v/>
+        <v>3.75</v>
       </c>
     </row>
     <row r="8" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2944,19 +2974,19 @@
       </c>
       <c r="C8" s="17">
         <f>COUNTIFS(Log!$D$6:$D$61,B8,Log!$H$6:$H$61,"Done")</f>
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D8" s="17">
         <f>SUMIFS(Log!$J$6:$J$61,Log!$D$6:$D$61,B8)</f>
-        <v>200</v>
+        <v>270</v>
       </c>
       <c r="E8" s="17">
         <f>SUMIFS(Log!$K$6:$K$61,Log!$D$6:$D$61,B8)</f>
-        <v>10.23</v>
-      </c>
-      <c r="F8" s="17" t="str">
+        <v>14.41</v>
+      </c>
+      <c r="F8" s="17">
         <f>IFERROR(AVERAGEIFS(Log!$O$6:$O$61,Log!$D$6:$D$61,B8,Log!$H$6:$H$61,"Done"),"")</f>
-        <v/>
+        <v>5.666666666666667</v>
       </c>
     </row>
     <row r="9" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3070,15 +3100,15 @@
       </c>
       <c r="C14" s="19">
         <f>SUM(C6:C13)</f>
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="D14" s="19">
         <f>SUM(D6:D13)</f>
-        <v>822</v>
+        <v>892</v>
       </c>
       <c r="E14" s="19">
         <f>SUM(E6:E13)</f>
-        <v>46.58</v>
+        <v>50.760000000000005</v>
       </c>
     </row>
   </sheetData>

--- a/Marathon_Training_Log.xlsx
+++ b/Marathon_Training_Log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Coursework\24-Git_Projects\02-Marathon_Training_Personal\Marathon_Training\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{040620A6-2116-4C2E-B71F-336EC0B2C5CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F84B61CF-036F-49E8-B1B8-732E8F3E07BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="106">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="107">
   <si>
     <t>Marathon Training Log — Pre-Super Base</t>
   </si>
@@ -361,6 +361,9 @@
   </si>
   <si>
     <t>Did Wednesday's run here.</t>
+  </si>
+  <si>
+    <t>Took rest to reset schedule and have long run on Saturday.</t>
   </si>
 </sst>
 </file>
@@ -1688,12 +1691,24 @@
       <c r="I23" s="14">
         <v>0</v>
       </c>
-      <c r="J23" s="9"/>
-      <c r="K23" s="9"/>
-      <c r="L23" s="9"/>
-      <c r="M23" s="9"/>
-      <c r="N23" s="9"/>
-      <c r="O23" s="9"/>
+      <c r="J23" s="9">
+        <v>0</v>
+      </c>
+      <c r="K23" s="9">
+        <v>0</v>
+      </c>
+      <c r="L23" s="9">
+        <v>0</v>
+      </c>
+      <c r="M23" s="9">
+        <v>0</v>
+      </c>
+      <c r="N23" s="9">
+        <v>0</v>
+      </c>
+      <c r="O23" s="9">
+        <v>0</v>
+      </c>
       <c r="P23" s="8" t="s">
         <v>105</v>
       </c>
@@ -1716,18 +1731,32 @@
       </c>
       <c r="G24" s="8"/>
       <c r="H24" s="9" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="I24" s="6">
         <v>50</v>
       </c>
-      <c r="J24" s="9"/>
-      <c r="K24" s="9"/>
-      <c r="L24" s="9"/>
-      <c r="M24" s="9"/>
-      <c r="N24" s="9"/>
-      <c r="O24" s="9"/>
-      <c r="P24" s="8"/>
+      <c r="J24" s="9">
+        <v>0</v>
+      </c>
+      <c r="K24" s="9">
+        <v>0</v>
+      </c>
+      <c r="L24" s="9">
+        <v>0</v>
+      </c>
+      <c r="M24" s="9">
+        <v>0</v>
+      </c>
+      <c r="N24" s="9">
+        <v>0</v>
+      </c>
+      <c r="O24" s="9">
+        <v>0</v>
+      </c>
+      <c r="P24" s="8" t="s">
+        <v>106</v>
+      </c>
     </row>
     <row r="25" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="10">
@@ -2974,7 +3003,7 @@
       </c>
       <c r="C8" s="17">
         <f>COUNTIFS(Log!$D$6:$D$61,B8,Log!$H$6:$H$61,"Done")</f>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D8" s="17">
         <f>SUMIFS(Log!$J$6:$J$61,Log!$D$6:$D$61,B8)</f>
@@ -2986,7 +3015,7 @@
       </c>
       <c r="F8" s="17">
         <f>IFERROR(AVERAGEIFS(Log!$O$6:$O$61,Log!$D$6:$D$61,B8,Log!$H$6:$H$61,"Done"),"")</f>
-        <v>5.666666666666667</v>
+        <v>3.4</v>
       </c>
     </row>
     <row r="9" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3100,7 +3129,7 @@
       </c>
       <c r="C14" s="19">
         <f>SUM(C6:C13)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D14" s="19">
         <f>SUM(D6:D13)</f>

--- a/Marathon_Training_Log.xlsx
+++ b/Marathon_Training_Log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Coursework\24-Git_Projects\02-Marathon_Training_Personal\Marathon_Training\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F84B61CF-036F-49E8-B1B8-732E8F3E07BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1086D0D-0AC0-40A4-BC04-B4D7CD0FBAFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="300" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="109">
   <si>
     <t>Marathon Training Log — Pre-Super Base</t>
   </si>
@@ -364,6 +364,12 @@
   </si>
   <si>
     <t>Took rest to reset schedule and have long run on Saturday.</t>
+  </si>
+  <si>
+    <t>10 min long run warm up with robin arzon + Hill blasts + 90 min Evening Run</t>
+  </si>
+  <si>
+    <t>Easy run really easy. Slowed down on hills section. Nose breathing. Did cooldown as walk. Hill blast section was followed after 10 min warmup.</t>
   </si>
 </sst>
 </file>
@@ -1774,20 +1780,36 @@
       <c r="F25" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="G25" s="8"/>
+      <c r="G25" s="8" t="s">
+        <v>107</v>
+      </c>
       <c r="H25" s="9" t="s">
         <v>27</v>
       </c>
       <c r="I25" s="11">
         <v>140</v>
       </c>
-      <c r="J25" s="9"/>
-      <c r="K25" s="9"/>
-      <c r="L25" s="9"/>
-      <c r="M25" s="9"/>
-      <c r="N25" s="9"/>
-      <c r="O25" s="9"/>
-      <c r="P25" s="8"/>
+      <c r="J25" s="9">
+        <v>125</v>
+      </c>
+      <c r="K25" s="9">
+        <v>7</v>
+      </c>
+      <c r="L25" s="9">
+        <v>16.22</v>
+      </c>
+      <c r="M25" s="9">
+        <v>136</v>
+      </c>
+      <c r="N25" s="9">
+        <v>152</v>
+      </c>
+      <c r="O25" s="9">
+        <v>3</v>
+      </c>
+      <c r="P25" s="8" t="s">
+        <v>108</v>
+      </c>
     </row>
     <row r="26" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="13">
@@ -3007,11 +3029,11 @@
       </c>
       <c r="D8" s="17">
         <f>SUMIFS(Log!$J$6:$J$61,Log!$D$6:$D$61,B8)</f>
-        <v>270</v>
+        <v>395</v>
       </c>
       <c r="E8" s="17">
         <f>SUMIFS(Log!$K$6:$K$61,Log!$D$6:$D$61,B8)</f>
-        <v>14.41</v>
+        <v>21.41</v>
       </c>
       <c r="F8" s="17">
         <f>IFERROR(AVERAGEIFS(Log!$O$6:$O$61,Log!$D$6:$D$61,B8,Log!$H$6:$H$61,"Done"),"")</f>
@@ -3133,11 +3155,11 @@
       </c>
       <c r="D14" s="19">
         <f>SUM(D6:D13)</f>
-        <v>892</v>
+        <v>1017</v>
       </c>
       <c r="E14" s="19">
         <f>SUM(E6:E13)</f>
-        <v>50.760000000000005</v>
+        <v>57.760000000000005</v>
       </c>
     </row>
   </sheetData>

--- a/Marathon_Training_Log.xlsx
+++ b/Marathon_Training_Log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Coursework\24-Git_Projects\02-Marathon_Training_Personal\Marathon_Training\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1086D0D-0AC0-40A4-BC04-B4D7CD0FBAFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0D9C460-DC16-4A55-9D94-780475D8EB50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1784,7 +1784,7 @@
         <v>107</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="I25" s="11">
         <v>140</v>
@@ -3025,7 +3025,7 @@
       </c>
       <c r="C8" s="17">
         <f>COUNTIFS(Log!$D$6:$D$61,B8,Log!$H$6:$H$61,"Done")</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D8" s="17">
         <f>SUMIFS(Log!$J$6:$J$61,Log!$D$6:$D$61,B8)</f>
@@ -3037,7 +3037,7 @@
       </c>
       <c r="F8" s="17">
         <f>IFERROR(AVERAGEIFS(Log!$O$6:$O$61,Log!$D$6:$D$61,B8,Log!$H$6:$H$61,"Done"),"")</f>
-        <v>3.4</v>
+        <v>3.3333333333333335</v>
       </c>
     </row>
     <row r="9" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="C14" s="19">
         <f>SUM(C6:C13)</f>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D14" s="19">
         <f>SUM(D6:D13)</f>

--- a/Marathon_Training_Log.xlsx
+++ b/Marathon_Training_Log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Coursework\24-Git_Projects\02-Marathon_Training_Personal\Marathon_Training\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0D9C460-DC16-4A55-9D94-780475D8EB50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B4BBD9C-88D7-4C62-AC3B-26AD64E3C89A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="111">
   <si>
     <t>Marathon Training Log — Pre-Super Base</t>
   </si>
@@ -370,6 +370,12 @@
   </si>
   <si>
     <t>Easy run really easy. Slowed down on hills section. Nose breathing. Did cooldown as walk. Hill blast section was followed after 10 min warmup.</t>
+  </si>
+  <si>
+    <t>Just took a walk</t>
+  </si>
+  <si>
+    <t>Just walk with dog</t>
   </si>
 </sst>
 </file>
@@ -1827,20 +1833,36 @@
       <c r="F26" s="15" t="s">
         <v>29</v>
       </c>
-      <c r="G26" s="8"/>
+      <c r="G26" s="8" t="s">
+        <v>109</v>
+      </c>
       <c r="H26" s="9" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="I26" s="14">
         <v>0</v>
       </c>
-      <c r="J26" s="9"/>
-      <c r="K26" s="9"/>
-      <c r="L26" s="9"/>
-      <c r="M26" s="9"/>
-      <c r="N26" s="9"/>
-      <c r="O26" s="9"/>
-      <c r="P26" s="8"/>
+      <c r="J26" s="9">
+        <v>36</v>
+      </c>
+      <c r="K26" s="9">
+        <v>1.41</v>
+      </c>
+      <c r="L26" s="9">
+        <v>2</v>
+      </c>
+      <c r="M26" s="9">
+        <v>100</v>
+      </c>
+      <c r="N26" s="9">
+        <v>114</v>
+      </c>
+      <c r="O26" s="9">
+        <v>1</v>
+      </c>
+      <c r="P26" s="8" t="s">
+        <v>110</v>
+      </c>
     </row>
     <row r="27" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="13">
@@ -3025,19 +3047,19 @@
       </c>
       <c r="C8" s="17">
         <f>COUNTIFS(Log!$D$6:$D$61,B8,Log!$H$6:$H$61,"Done")</f>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D8" s="17">
         <f>SUMIFS(Log!$J$6:$J$61,Log!$D$6:$D$61,B8)</f>
-        <v>395</v>
+        <v>431</v>
       </c>
       <c r="E8" s="17">
         <f>SUMIFS(Log!$K$6:$K$61,Log!$D$6:$D$61,B8)</f>
-        <v>21.41</v>
+        <v>22.82</v>
       </c>
       <c r="F8" s="17">
         <f>IFERROR(AVERAGEIFS(Log!$O$6:$O$61,Log!$D$6:$D$61,B8,Log!$H$6:$H$61,"Done"),"")</f>
-        <v>3.3333333333333335</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3151,15 +3173,15 @@
       </c>
       <c r="C14" s="19">
         <f>SUM(C6:C13)</f>
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D14" s="19">
         <f>SUM(D6:D13)</f>
-        <v>1017</v>
+        <v>1053</v>
       </c>
       <c r="E14" s="19">
         <f>SUM(E6:E13)</f>
-        <v>57.760000000000005</v>
+        <v>59.17</v>
       </c>
     </row>
   </sheetData>

--- a/Marathon_Training_Log.xlsx
+++ b/Marathon_Training_Log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Coursework\24-Git_Projects\02-Marathon_Training_Personal\Marathon_Training\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B4BBD9C-88D7-4C62-AC3B-26AD64E3C89A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2328B193-606B-4AD8-8991-A385DDED014A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="113">
   <si>
     <t>Marathon Training Log — Pre-Super Base</t>
   </si>
@@ -376,6 +376,12 @@
   </si>
   <si>
     <t>Just walk with dog</t>
+  </si>
+  <si>
+    <t>30 min Strength for Runners with Rebecca Kennedy</t>
+  </si>
+  <si>
+    <t>20lb max weight training with focus on squats.</t>
   </si>
 </sst>
 </file>
@@ -1880,20 +1886,36 @@
       <c r="F27" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="G27" s="8"/>
+      <c r="G27" s="8" t="s">
+        <v>111</v>
+      </c>
       <c r="H27" s="9" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="I27" s="14">
         <v>0</v>
       </c>
-      <c r="J27" s="9"/>
-      <c r="K27" s="9"/>
-      <c r="L27" s="9"/>
-      <c r="M27" s="9"/>
-      <c r="N27" s="9"/>
-      <c r="O27" s="9"/>
-      <c r="P27" s="8"/>
+      <c r="J27" s="9">
+        <v>32</v>
+      </c>
+      <c r="K27" s="9">
+        <v>0</v>
+      </c>
+      <c r="L27" s="9">
+        <v>0</v>
+      </c>
+      <c r="M27" s="9">
+        <v>122</v>
+      </c>
+      <c r="N27" s="9">
+        <v>150</v>
+      </c>
+      <c r="O27" s="9">
+        <v>3</v>
+      </c>
+      <c r="P27" s="8" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="28" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="5">
@@ -3068,19 +3090,19 @@
       </c>
       <c r="C9" s="17">
         <f>COUNTIFS(Log!$D$6:$D$61,B9,Log!$H$6:$H$61,"Done")</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" s="17">
         <f>SUMIFS(Log!$J$6:$J$61,Log!$D$6:$D$61,B9)</f>
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="E9" s="17">
         <f>SUMIFS(Log!$K$6:$K$61,Log!$D$6:$D$61,B9)</f>
         <v>0</v>
       </c>
-      <c r="F9" s="17" t="str">
+      <c r="F9" s="17">
         <f>IFERROR(AVERAGEIFS(Log!$O$6:$O$61,Log!$D$6:$D$61,B9,Log!$H$6:$H$61,"Done"),"")</f>
-        <v/>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3173,11 +3195,11 @@
       </c>
       <c r="C14" s="19">
         <f>SUM(C6:C13)</f>
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="D14" s="19">
         <f>SUM(D6:D13)</f>
-        <v>1053</v>
+        <v>1085</v>
       </c>
       <c r="E14" s="19">
         <f>SUM(E6:E13)</f>

--- a/Marathon_Training_Log.xlsx
+++ b/Marathon_Training_Log.xlsx
@@ -5,19 +5,19 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Coursework\24-Git_Projects\02-Marathon_Training_Personal\Marathon_Training\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\psaptarshi\Downloads\Marathon_Training-main\Marathon_Training-main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2328B193-606B-4AD8-8991-A385DDED014A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7369C00D-C106-4562-A2D6-7856CF8ACAE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Log" sheetId="1" r:id="rId1"/>
     <sheet name="Weekly Summary" sheetId="2" r:id="rId2"/>
     <sheet name="Session Guide" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="306" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="115">
   <si>
     <t>Marathon Training Log — Pre-Super Base</t>
   </si>
@@ -382,6 +382,12 @@
   </si>
   <si>
     <t>20lb max weight training with focus on squats.</t>
+  </si>
+  <si>
+    <t>10 min warmup + 45 min class + 30 min class with last 10 min in cooldown</t>
+  </si>
+  <si>
+    <t>Very slow running. Did hit some hills so heart rate spiked during that time. But mostly the heart rate was below 148 bpm.</t>
   </si>
 </sst>
 </file>
@@ -817,28 +823,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:P61"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="43.140625" customWidth="1"/>
-    <col min="3" max="3" width="4.85546875" customWidth="1"/>
-    <col min="4" max="4" width="3.85546875" customWidth="1"/>
-    <col min="5" max="5" width="15.28515625" customWidth="1"/>
+    <col min="2" max="2" width="43.1796875" customWidth="1"/>
+    <col min="3" max="3" width="4.81640625" customWidth="1"/>
+    <col min="4" max="4" width="3.81640625" customWidth="1"/>
+    <col min="5" max="5" width="15.26953125" customWidth="1"/>
     <col min="6" max="6" width="111" customWidth="1"/>
-    <col min="7" max="7" width="71.5703125" customWidth="1"/>
-    <col min="8" max="8" width="7.7109375" customWidth="1"/>
-    <col min="12" max="12" width="9.5703125" customWidth="1"/>
-    <col min="13" max="13" width="7.5703125" customWidth="1"/>
+    <col min="7" max="7" width="71.54296875" customWidth="1"/>
+    <col min="8" max="8" width="7.7265625" customWidth="1"/>
+    <col min="12" max="12" width="9.54296875" customWidth="1"/>
+    <col min="13" max="13" width="7.54296875" customWidth="1"/>
     <col min="14" max="14" width="8" customWidth="1"/>
-    <col min="15" max="15" width="7.140625" customWidth="1"/>
-    <col min="16" max="16" width="73.5703125" customWidth="1"/>
+    <col min="15" max="15" width="7.1796875" customWidth="1"/>
+    <col min="16" max="16" width="73.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="2:16" s="2" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:16" s="2" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
@@ -846,7 +852,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="2:16" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:16" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="4" t="s">
         <v>3</v>
       </c>
@@ -893,7 +899,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="2:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B6" s="5">
         <v>46230</v>
       </c>
@@ -940,7 +946,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="2:16" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:16" ht="93.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="10">
         <v>46231</v>
       </c>
@@ -987,7 +993,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="8" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="13">
         <v>46232</v>
       </c>
@@ -1034,7 +1040,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="9" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="5">
         <v>46233</v>
       </c>
@@ -1081,7 +1087,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="10" spans="2:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="10">
         <v>46234</v>
       </c>
@@ -1128,7 +1134,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="11" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="10">
         <v>46235</v>
       </c>
@@ -1175,7 +1181,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="12" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="13">
         <v>46236</v>
       </c>
@@ -1222,7 +1228,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="13" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="13">
         <v>46237</v>
       </c>
@@ -1269,7 +1275,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="14" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="5">
         <v>46238</v>
       </c>
@@ -1316,7 +1322,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="15" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="10">
         <v>46239</v>
       </c>
@@ -1363,7 +1369,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="16" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B16" s="13">
         <v>46240</v>
       </c>
@@ -1408,7 +1414,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="17" spans="2:16" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:16" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="5">
         <v>46241</v>
       </c>
@@ -1453,7 +1459,7 @@
       </c>
       <c r="P17" s="8"/>
     </row>
-    <row r="18" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="10">
         <v>46242</v>
       </c>
@@ -1500,7 +1506,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="19" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B19" s="13">
         <v>46243</v>
       </c>
@@ -1545,7 +1551,7 @@
       </c>
       <c r="P19" s="8"/>
     </row>
-    <row r="20" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B20" s="13">
         <v>46244</v>
       </c>
@@ -1592,7 +1598,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B21" s="5">
         <v>46245</v>
       </c>
@@ -1639,7 +1645,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="22" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B22" s="10">
         <v>46246</v>
       </c>
@@ -1686,7 +1692,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="23" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B23" s="13">
         <v>46247</v>
       </c>
@@ -1731,7 +1737,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="24" spans="2:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B24" s="5">
         <v>46248</v>
       </c>
@@ -1776,7 +1782,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="25" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B25" s="10">
         <v>46249</v>
       </c>
@@ -1823,7 +1829,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="26" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B26" s="13">
         <v>46250</v>
       </c>
@@ -1870,7 +1876,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="27" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B27" s="13">
         <v>46251</v>
       </c>
@@ -1917,7 +1923,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="28" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B28" s="5">
         <v>46252</v>
       </c>
@@ -1933,22 +1939,38 @@
       <c r="F28" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="G28" s="8"/>
+      <c r="G28" s="8" t="s">
+        <v>113</v>
+      </c>
       <c r="H28" s="9" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="I28" s="6">
         <v>65</v>
       </c>
-      <c r="J28" s="9"/>
-      <c r="K28" s="9"/>
-      <c r="L28" s="9"/>
-      <c r="M28" s="9"/>
-      <c r="N28" s="9"/>
-      <c r="O28" s="9"/>
-      <c r="P28" s="8"/>
-    </row>
-    <row r="29" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="J28" s="9">
+        <v>70</v>
+      </c>
+      <c r="K28" s="9">
+        <v>5</v>
+      </c>
+      <c r="L28" s="9">
+        <v>14.3</v>
+      </c>
+      <c r="M28" s="9">
+        <v>132</v>
+      </c>
+      <c r="N28" s="9">
+        <v>158</v>
+      </c>
+      <c r="O28" s="9">
+        <v>3.5</v>
+      </c>
+      <c r="P28" s="8" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="29" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B29" s="10">
         <v>46253</v>
       </c>
@@ -1979,7 +2001,7 @@
       <c r="O29" s="9"/>
       <c r="P29" s="8"/>
     </row>
-    <row r="30" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B30" s="13">
         <v>46254</v>
       </c>
@@ -2010,7 +2032,7 @@
       <c r="O30" s="9"/>
       <c r="P30" s="8"/>
     </row>
-    <row r="31" spans="2:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B31" s="5">
         <v>46255</v>
       </c>
@@ -2041,7 +2063,7 @@
       <c r="O31" s="9"/>
       <c r="P31" s="8"/>
     </row>
-    <row r="32" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B32" s="10">
         <v>46256</v>
       </c>
@@ -2072,7 +2094,7 @@
       <c r="O32" s="9"/>
       <c r="P32" s="8"/>
     </row>
-    <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B33" s="13">
         <v>46257</v>
       </c>
@@ -2103,7 +2125,7 @@
       <c r="O33" s="9"/>
       <c r="P33" s="8"/>
     </row>
-    <row r="34" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B34" s="13">
         <v>46258</v>
       </c>
@@ -2134,7 +2156,7 @@
       <c r="O34" s="9"/>
       <c r="P34" s="8"/>
     </row>
-    <row r="35" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B35" s="5">
         <v>46259</v>
       </c>
@@ -2165,7 +2187,7 @@
       <c r="O35" s="9"/>
       <c r="P35" s="8"/>
     </row>
-    <row r="36" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B36" s="10">
         <v>46260</v>
       </c>
@@ -2196,7 +2218,7 @@
       <c r="O36" s="9"/>
       <c r="P36" s="8"/>
     </row>
-    <row r="37" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B37" s="13">
         <v>46261</v>
       </c>
@@ -2227,7 +2249,7 @@
       <c r="O37" s="9"/>
       <c r="P37" s="8"/>
     </row>
-    <row r="38" spans="2:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B38" s="5">
         <v>46262</v>
       </c>
@@ -2258,7 +2280,7 @@
       <c r="O38" s="9"/>
       <c r="P38" s="8"/>
     </row>
-    <row r="39" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B39" s="10">
         <v>46263</v>
       </c>
@@ -2289,7 +2311,7 @@
       <c r="O39" s="9"/>
       <c r="P39" s="8"/>
     </row>
-    <row r="40" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B40" s="13">
         <v>46264</v>
       </c>
@@ -2320,7 +2342,7 @@
       <c r="O40" s="9"/>
       <c r="P40" s="8"/>
     </row>
-    <row r="41" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B41" s="13">
         <v>46265</v>
       </c>
@@ -2351,7 +2373,7 @@
       <c r="O41" s="9"/>
       <c r="P41" s="8"/>
     </row>
-    <row r="42" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B42" s="5">
         <v>46266</v>
       </c>
@@ -2382,7 +2404,7 @@
       <c r="O42" s="9"/>
       <c r="P42" s="8"/>
     </row>
-    <row r="43" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B43" s="10">
         <v>46267</v>
       </c>
@@ -2413,7 +2435,7 @@
       <c r="O43" s="9"/>
       <c r="P43" s="8"/>
     </row>
-    <row r="44" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B44" s="13">
         <v>46268</v>
       </c>
@@ -2444,7 +2466,7 @@
       <c r="O44" s="9"/>
       <c r="P44" s="8"/>
     </row>
-    <row r="45" spans="2:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B45" s="5">
         <v>46269</v>
       </c>
@@ -2475,7 +2497,7 @@
       <c r="O45" s="9"/>
       <c r="P45" s="8"/>
     </row>
-    <row r="46" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B46" s="10">
         <v>46270</v>
       </c>
@@ -2506,7 +2528,7 @@
       <c r="O46" s="9"/>
       <c r="P46" s="8"/>
     </row>
-    <row r="47" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B47" s="13">
         <v>46271</v>
       </c>
@@ -2537,7 +2559,7 @@
       <c r="O47" s="9"/>
       <c r="P47" s="8"/>
     </row>
-    <row r="48" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B48" s="13">
         <v>46272</v>
       </c>
@@ -2568,7 +2590,7 @@
       <c r="O48" s="9"/>
       <c r="P48" s="8"/>
     </row>
-    <row r="49" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B49" s="5">
         <v>46273</v>
       </c>
@@ -2599,7 +2621,7 @@
       <c r="O49" s="9"/>
       <c r="P49" s="8"/>
     </row>
-    <row r="50" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B50" s="10">
         <v>46274</v>
       </c>
@@ -2630,7 +2652,7 @@
       <c r="O50" s="9"/>
       <c r="P50" s="8"/>
     </row>
-    <row r="51" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B51" s="13">
         <v>46275</v>
       </c>
@@ -2661,7 +2683,7 @@
       <c r="O51" s="9"/>
       <c r="P51" s="8"/>
     </row>
-    <row r="52" spans="2:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B52" s="5">
         <v>46276</v>
       </c>
@@ -2692,7 +2714,7 @@
       <c r="O52" s="9"/>
       <c r="P52" s="8"/>
     </row>
-    <row r="53" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B53" s="10">
         <v>46277</v>
       </c>
@@ -2723,7 +2745,7 @@
       <c r="O53" s="9"/>
       <c r="P53" s="8"/>
     </row>
-    <row r="54" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B54" s="13">
         <v>46278</v>
       </c>
@@ -2754,7 +2776,7 @@
       <c r="O54" s="9"/>
       <c r="P54" s="8"/>
     </row>
-    <row r="55" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B55" s="13">
         <v>46279</v>
       </c>
@@ -2785,7 +2807,7 @@
       <c r="O55" s="9"/>
       <c r="P55" s="8"/>
     </row>
-    <row r="56" spans="2:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B56" s="5">
         <v>46280</v>
       </c>
@@ -2816,7 +2838,7 @@
       <c r="O56" s="9"/>
       <c r="P56" s="8"/>
     </row>
-    <row r="57" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B57" s="10">
         <v>46281</v>
       </c>
@@ -2847,7 +2869,7 @@
       <c r="O57" s="9"/>
       <c r="P57" s="8"/>
     </row>
-    <row r="58" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B58" s="13">
         <v>46282</v>
       </c>
@@ -2878,7 +2900,7 @@
       <c r="O58" s="9"/>
       <c r="P58" s="8"/>
     </row>
-    <row r="59" spans="2:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B59" s="5">
         <v>46283</v>
       </c>
@@ -2909,7 +2931,7 @@
       <c r="O59" s="9"/>
       <c r="P59" s="8"/>
     </row>
-    <row r="60" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B60" s="10">
         <v>46284</v>
       </c>
@@ -2940,7 +2962,7 @@
       <c r="O60" s="9"/>
       <c r="P60" s="8"/>
     </row>
-    <row r="61" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B61" s="13">
         <v>46285</v>
       </c>
@@ -2986,7 +3008,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B2:F14"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="8" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
@@ -2994,17 +3016,17 @@
     <col min="6" max="6" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="3" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="16" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="5" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="4" t="s">
         <v>5</v>
       </c>
@@ -3021,7 +3043,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="6" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B6" s="17">
         <v>1</v>
       </c>
@@ -3042,7 +3064,7 @@
         <v>4.833333333333333</v>
       </c>
     </row>
-    <row r="7" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="17">
         <v>2</v>
       </c>
@@ -3063,7 +3085,7 @@
         <v>3.75</v>
       </c>
     </row>
-    <row r="8" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="17">
         <v>3</v>
       </c>
@@ -3084,28 +3106,28 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="17">
         <v>4</v>
       </c>
       <c r="C9" s="17">
         <f>COUNTIFS(Log!$D$6:$D$61,B9,Log!$H$6:$H$61,"Done")</f>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D9" s="17">
         <f>SUMIFS(Log!$J$6:$J$61,Log!$D$6:$D$61,B9)</f>
-        <v>32</v>
+        <v>102</v>
       </c>
       <c r="E9" s="17">
         <f>SUMIFS(Log!$K$6:$K$61,Log!$D$6:$D$61,B9)</f>
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F9" s="17">
         <f>IFERROR(AVERAGEIFS(Log!$O$6:$O$61,Log!$D$6:$D$61,B9,Log!$H$6:$H$61,"Done"),"")</f>
-        <v>3</v>
-      </c>
-    </row>
-    <row r="10" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>3.25</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B10" s="17">
         <v>5</v>
       </c>
@@ -3126,7 +3148,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="17">
         <v>6</v>
       </c>
@@ -3147,7 +3169,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B12" s="17">
         <v>7</v>
       </c>
@@ -3168,7 +3190,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="17">
         <v>8</v>
       </c>
@@ -3189,21 +3211,21 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B14" s="18" t="s">
         <v>58</v>
       </c>
       <c r="C14" s="19">
         <f>SUM(C6:C13)</f>
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="D14" s="19">
         <f>SUM(D6:D13)</f>
-        <v>1085</v>
+        <v>1155</v>
       </c>
       <c r="E14" s="19">
         <f>SUM(E6:E13)</f>
-        <v>59.17</v>
+        <v>64.17</v>
       </c>
     </row>
   </sheetData>
@@ -3215,23 +3237,23 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B2:C17"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="26" customWidth="1"/>
     <col min="3" max="3" width="95" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="B2" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="16" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="2:3" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:3" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B5" s="20" t="s">
         <v>61</v>
       </c>
@@ -3239,7 +3261,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="7" spans="2:3" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:3" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B7" s="20" t="s">
         <v>63</v>
       </c>
@@ -3247,7 +3269,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="9" spans="2:3" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:3" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B9" s="20" t="s">
         <v>65</v>
       </c>
@@ -3255,7 +3277,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="11" spans="2:3" ht="70.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:3" ht="70.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B11" s="20" t="s">
         <v>67</v>
       </c>
@@ -3263,7 +3285,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="13" spans="2:3" ht="77.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:3" ht="77.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B13" s="20" t="s">
         <v>69</v>
       </c>
@@ -3271,7 +3293,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="2:3" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:3" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B15" s="20" t="s">
         <v>71</v>
       </c>
@@ -3279,7 +3301,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="17" spans="2:3" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:3" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="20" t="s">
         <v>73</v>
       </c>

--- a/Marathon_Training_Log.xlsx
+++ b/Marathon_Training_Log.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\psaptarshi\Downloads\Marathon_Training-main\Marathon_Training-main\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Coursework\24-Git_Projects\02-Marathon_Training_Personal\Marathon_Training\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7369C00D-C106-4562-A2D6-7856CF8ACAE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4306A78F-BF6D-494A-8191-D778F9250375}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Log" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="117">
   <si>
     <t>Marathon Training Log — Pre-Super Base</t>
   </si>
@@ -388,6 +388,18 @@
   </si>
   <si>
     <t>Very slow running. Did hit some hills so heart rate spiked during that time. But mostly the heart rate was below 148 bpm.</t>
+  </si>
+  <si>
+    <t>15 min warmup + 45 min Tempo Run with Becs Gentry + 10 min coolodown</t>
+  </si>
+  <si>
+    <t>15 min very slow run at 3 miles/hr
+Followed by the set.
+1st set: Ran at 6 miles/hr with 0.5% incline. Not terrible, but found needing more and more time to recover heartrate back to around 130s. So dropped. RPE 6.5
+2nd set: Ran at 5.8 miles/hr with 0.5% incline. Felt better. RPE 6.5
+3rd set: Ran at 5.8 miles/hr with 0% incline. Stress felt similar to RPE 6.5
+After each run, jogged at 3 miles/hr for 2min 20 sec.
+Between each set jogged at 3 miles/hr for almost 4 min.</t>
   </si>
 </sst>
 </file>
@@ -823,28 +835,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B2:P61"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="43.1796875" customWidth="1"/>
-    <col min="3" max="3" width="4.81640625" customWidth="1"/>
-    <col min="4" max="4" width="3.81640625" customWidth="1"/>
-    <col min="5" max="5" width="15.26953125" customWidth="1"/>
+    <col min="2" max="2" width="43.140625" customWidth="1"/>
+    <col min="3" max="3" width="4.85546875" customWidth="1"/>
+    <col min="4" max="4" width="3.85546875" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" customWidth="1"/>
     <col min="6" max="6" width="111" customWidth="1"/>
-    <col min="7" max="7" width="71.54296875" customWidth="1"/>
-    <col min="8" max="8" width="7.7265625" customWidth="1"/>
-    <col min="12" max="12" width="9.54296875" customWidth="1"/>
-    <col min="13" max="13" width="7.54296875" customWidth="1"/>
+    <col min="7" max="7" width="71.5703125" customWidth="1"/>
+    <col min="8" max="8" width="7.7109375" customWidth="1"/>
+    <col min="12" max="12" width="9.5703125" customWidth="1"/>
+    <col min="13" max="13" width="7.5703125" customWidth="1"/>
     <col min="14" max="14" width="8" customWidth="1"/>
-    <col min="15" max="15" width="7.1796875" customWidth="1"/>
-    <col min="16" max="16" width="73.54296875" customWidth="1"/>
+    <col min="15" max="15" width="7.140625" customWidth="1"/>
+    <col min="16" max="16" width="73.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="2:16" s="2" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:16" s="2" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
@@ -852,7 +864,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="2:16" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:16" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
         <v>3</v>
       </c>
@@ -899,7 +911,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="2:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="5">
         <v>46230</v>
       </c>
@@ -946,7 +958,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="2:16" ht="93.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:16" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="10">
         <v>46231</v>
       </c>
@@ -993,7 +1005,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="8" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="13">
         <v>46232</v>
       </c>
@@ -1040,7 +1052,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="9" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="5">
         <v>46233</v>
       </c>
@@ -1087,7 +1099,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="10" spans="2:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="10">
         <v>46234</v>
       </c>
@@ -1134,7 +1146,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="11" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="10">
         <v>46235</v>
       </c>
@@ -1181,7 +1193,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="12" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="13">
         <v>46236</v>
       </c>
@@ -1228,7 +1240,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="13" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="13">
         <v>46237</v>
       </c>
@@ -1275,7 +1287,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="14" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="5">
         <v>46238</v>
       </c>
@@ -1322,7 +1334,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="15" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="10">
         <v>46239</v>
       </c>
@@ -1369,7 +1381,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="16" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="13">
         <v>46240</v>
       </c>
@@ -1414,7 +1426,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="17" spans="2:16" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:16" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="5">
         <v>46241</v>
       </c>
@@ -1459,7 +1471,7 @@
       </c>
       <c r="P17" s="8"/>
     </row>
-    <row r="18" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="10">
         <v>46242</v>
       </c>
@@ -1506,7 +1518,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="19" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="13">
         <v>46243</v>
       </c>
@@ -1551,7 +1563,7 @@
       </c>
       <c r="P19" s="8"/>
     </row>
-    <row r="20" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="13">
         <v>46244</v>
       </c>
@@ -1598,7 +1610,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="5">
         <v>46245</v>
       </c>
@@ -1645,7 +1657,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="22" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="10">
         <v>46246</v>
       </c>
@@ -1692,7 +1704,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="23" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="13">
         <v>46247</v>
       </c>
@@ -1737,7 +1749,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="24" spans="2:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="5">
         <v>46248</v>
       </c>
@@ -1782,7 +1794,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="25" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="10">
         <v>46249</v>
       </c>
@@ -1829,7 +1841,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="26" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="13">
         <v>46250</v>
       </c>
@@ -1876,7 +1888,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="27" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="13">
         <v>46251</v>
       </c>
@@ -1923,7 +1935,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="28" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="5">
         <v>46252</v>
       </c>
@@ -1970,7 +1982,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="29" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:16" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="10">
         <v>46253</v>
       </c>
@@ -1986,22 +1998,38 @@
       <c r="F29" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="G29" s="8"/>
+      <c r="G29" s="8" t="s">
+        <v>115</v>
+      </c>
       <c r="H29" s="9" t="s">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="I29" s="11">
         <v>57</v>
       </c>
-      <c r="J29" s="9"/>
-      <c r="K29" s="9"/>
-      <c r="L29" s="9"/>
-      <c r="M29" s="9"/>
-      <c r="N29" s="9"/>
-      <c r="O29" s="9"/>
-      <c r="P29" s="8"/>
-    </row>
-    <row r="30" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="J29" s="9">
+        <v>70</v>
+      </c>
+      <c r="K29" s="9">
+        <v>4</v>
+      </c>
+      <c r="L29" s="9">
+        <v>18.29</v>
+      </c>
+      <c r="M29" s="9">
+        <v>144</v>
+      </c>
+      <c r="N29" s="9">
+        <v>172</v>
+      </c>
+      <c r="O29" s="9">
+        <v>6.5</v>
+      </c>
+      <c r="P29" s="8" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="30" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="13">
         <v>46254</v>
       </c>
@@ -2032,7 +2060,7 @@
       <c r="O30" s="9"/>
       <c r="P30" s="8"/>
     </row>
-    <row r="31" spans="2:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="5">
         <v>46255</v>
       </c>
@@ -2063,7 +2091,7 @@
       <c r="O31" s="9"/>
       <c r="P31" s="8"/>
     </row>
-    <row r="32" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="10">
         <v>46256</v>
       </c>
@@ -2094,7 +2122,7 @@
       <c r="O32" s="9"/>
       <c r="P32" s="8"/>
     </row>
-    <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B33" s="13">
         <v>46257</v>
       </c>
@@ -2125,7 +2153,7 @@
       <c r="O33" s="9"/>
       <c r="P33" s="8"/>
     </row>
-    <row r="34" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B34" s="13">
         <v>46258</v>
       </c>
@@ -2156,7 +2184,7 @@
       <c r="O34" s="9"/>
       <c r="P34" s="8"/>
     </row>
-    <row r="35" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="5">
         <v>46259</v>
       </c>
@@ -2187,7 +2215,7 @@
       <c r="O35" s="9"/>
       <c r="P35" s="8"/>
     </row>
-    <row r="36" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B36" s="10">
         <v>46260</v>
       </c>
@@ -2218,7 +2246,7 @@
       <c r="O36" s="9"/>
       <c r="P36" s="8"/>
     </row>
-    <row r="37" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B37" s="13">
         <v>46261</v>
       </c>
@@ -2249,7 +2277,7 @@
       <c r="O37" s="9"/>
       <c r="P37" s="8"/>
     </row>
-    <row r="38" spans="2:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B38" s="5">
         <v>46262</v>
       </c>
@@ -2280,7 +2308,7 @@
       <c r="O38" s="9"/>
       <c r="P38" s="8"/>
     </row>
-    <row r="39" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B39" s="10">
         <v>46263</v>
       </c>
@@ -2311,7 +2339,7 @@
       <c r="O39" s="9"/>
       <c r="P39" s="8"/>
     </row>
-    <row r="40" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B40" s="13">
         <v>46264</v>
       </c>
@@ -2342,7 +2370,7 @@
       <c r="O40" s="9"/>
       <c r="P40" s="8"/>
     </row>
-    <row r="41" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B41" s="13">
         <v>46265</v>
       </c>
@@ -2373,7 +2401,7 @@
       <c r="O41" s="9"/>
       <c r="P41" s="8"/>
     </row>
-    <row r="42" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B42" s="5">
         <v>46266</v>
       </c>
@@ -2404,7 +2432,7 @@
       <c r="O42" s="9"/>
       <c r="P42" s="8"/>
     </row>
-    <row r="43" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B43" s="10">
         <v>46267</v>
       </c>
@@ -2435,7 +2463,7 @@
       <c r="O43" s="9"/>
       <c r="P43" s="8"/>
     </row>
-    <row r="44" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B44" s="13">
         <v>46268</v>
       </c>
@@ -2466,7 +2494,7 @@
       <c r="O44" s="9"/>
       <c r="P44" s="8"/>
     </row>
-    <row r="45" spans="2:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B45" s="5">
         <v>46269</v>
       </c>
@@ -2497,7 +2525,7 @@
       <c r="O45" s="9"/>
       <c r="P45" s="8"/>
     </row>
-    <row r="46" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B46" s="10">
         <v>46270</v>
       </c>
@@ -2528,7 +2556,7 @@
       <c r="O46" s="9"/>
       <c r="P46" s="8"/>
     </row>
-    <row r="47" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B47" s="13">
         <v>46271</v>
       </c>
@@ -2559,7 +2587,7 @@
       <c r="O47" s="9"/>
       <c r="P47" s="8"/>
     </row>
-    <row r="48" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B48" s="13">
         <v>46272</v>
       </c>
@@ -2590,7 +2618,7 @@
       <c r="O48" s="9"/>
       <c r="P48" s="8"/>
     </row>
-    <row r="49" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B49" s="5">
         <v>46273</v>
       </c>
@@ -2621,7 +2649,7 @@
       <c r="O49" s="9"/>
       <c r="P49" s="8"/>
     </row>
-    <row r="50" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B50" s="10">
         <v>46274</v>
       </c>
@@ -2652,7 +2680,7 @@
       <c r="O50" s="9"/>
       <c r="P50" s="8"/>
     </row>
-    <row r="51" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="13">
         <v>46275</v>
       </c>
@@ -2683,7 +2711,7 @@
       <c r="O51" s="9"/>
       <c r="P51" s="8"/>
     </row>
-    <row r="52" spans="2:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B52" s="5">
         <v>46276</v>
       </c>
@@ -2714,7 +2742,7 @@
       <c r="O52" s="9"/>
       <c r="P52" s="8"/>
     </row>
-    <row r="53" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B53" s="10">
         <v>46277</v>
       </c>
@@ -2745,7 +2773,7 @@
       <c r="O53" s="9"/>
       <c r="P53" s="8"/>
     </row>
-    <row r="54" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B54" s="13">
         <v>46278</v>
       </c>
@@ -2776,7 +2804,7 @@
       <c r="O54" s="9"/>
       <c r="P54" s="8"/>
     </row>
-    <row r="55" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B55" s="13">
         <v>46279</v>
       </c>
@@ -2807,7 +2835,7 @@
       <c r="O55" s="9"/>
       <c r="P55" s="8"/>
     </row>
-    <row r="56" spans="2:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B56" s="5">
         <v>46280</v>
       </c>
@@ -2838,7 +2866,7 @@
       <c r="O56" s="9"/>
       <c r="P56" s="8"/>
     </row>
-    <row r="57" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B57" s="10">
         <v>46281</v>
       </c>
@@ -2869,7 +2897,7 @@
       <c r="O57" s="9"/>
       <c r="P57" s="8"/>
     </row>
-    <row r="58" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B58" s="13">
         <v>46282</v>
       </c>
@@ -2900,7 +2928,7 @@
       <c r="O58" s="9"/>
       <c r="P58" s="8"/>
     </row>
-    <row r="59" spans="2:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B59" s="5">
         <v>46283</v>
       </c>
@@ -2931,7 +2959,7 @@
       <c r="O59" s="9"/>
       <c r="P59" s="8"/>
     </row>
-    <row r="60" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B60" s="10">
         <v>46284</v>
       </c>
@@ -2962,7 +2990,7 @@
       <c r="O60" s="9"/>
       <c r="P60" s="8"/>
     </row>
-    <row r="61" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B61" s="13">
         <v>46285</v>
       </c>
@@ -3008,7 +3036,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="B2:F14"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="8" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
@@ -3016,17 +3044,17 @@
     <col min="6" max="6" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="3" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="16" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="5" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
         <v>5</v>
       </c>
@@ -3043,7 +3071,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="6" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="17">
         <v>1</v>
       </c>
@@ -3064,7 +3092,7 @@
         <v>4.833333333333333</v>
       </c>
     </row>
-    <row r="7" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="17">
         <v>2</v>
       </c>
@@ -3085,7 +3113,7 @@
         <v>3.75</v>
       </c>
     </row>
-    <row r="8" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="17">
         <v>3</v>
       </c>
@@ -3106,28 +3134,28 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="17">
         <v>4</v>
       </c>
       <c r="C9" s="17">
         <f>COUNTIFS(Log!$D$6:$D$61,B9,Log!$H$6:$H$61,"Done")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" s="17">
         <f>SUMIFS(Log!$J$6:$J$61,Log!$D$6:$D$61,B9)</f>
-        <v>102</v>
+        <v>172</v>
       </c>
       <c r="E9" s="17">
         <f>SUMIFS(Log!$K$6:$K$61,Log!$D$6:$D$61,B9)</f>
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F9" s="17">
         <f>IFERROR(AVERAGEIFS(Log!$O$6:$O$61,Log!$D$6:$D$61,B9,Log!$H$6:$H$61,"Done"),"")</f>
-        <v>3.25</v>
-      </c>
-    </row>
-    <row r="10" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+        <v>4.333333333333333</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="17">
         <v>5</v>
       </c>
@@ -3148,7 +3176,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="17">
         <v>6</v>
       </c>
@@ -3169,7 +3197,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="17">
         <v>7</v>
       </c>
@@ -3190,7 +3218,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="17">
         <v>8</v>
       </c>
@@ -3211,21 +3239,21 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="18" t="s">
         <v>58</v>
       </c>
       <c r="C14" s="19">
         <f>SUM(C6:C13)</f>
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="D14" s="19">
         <f>SUM(D6:D13)</f>
-        <v>1155</v>
+        <v>1225</v>
       </c>
       <c r="E14" s="19">
         <f>SUM(E6:E13)</f>
-        <v>64.17</v>
+        <v>68.17</v>
       </c>
     </row>
   </sheetData>
@@ -3237,23 +3265,23 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B2:C17"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="26" customWidth="1"/>
     <col min="3" max="3" width="95" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="3" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="16" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="2:3" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:3" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="20" t="s">
         <v>61</v>
       </c>
@@ -3261,7 +3289,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="7" spans="2:3" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="2:3" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="20" t="s">
         <v>63</v>
       </c>
@@ -3269,7 +3297,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="9" spans="2:3" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="2:3" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="20" t="s">
         <v>65</v>
       </c>
@@ -3277,7 +3305,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="11" spans="2:3" ht="70.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="2:3" ht="70.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="20" t="s">
         <v>67</v>
       </c>
@@ -3285,7 +3313,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="13" spans="2:3" ht="77.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="2:3" ht="77.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="20" t="s">
         <v>69</v>
       </c>
@@ -3293,7 +3321,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="15" spans="2:3" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:3" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="20" t="s">
         <v>71</v>
       </c>
@@ -3301,7 +3329,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="17" spans="2:3" ht="45.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:3" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="20" t="s">
         <v>73</v>
       </c>

--- a/Marathon_Training_Log.xlsx
+++ b/Marathon_Training_Log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Coursework\24-Git_Projects\02-Marathon_Training_Personal\Marathon_Training\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4306A78F-BF6D-494A-8191-D778F9250375}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A57E01A7-8299-47B1-9FCB-BE8E7ACECBFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -398,6 +398,7 @@
 1st set: Ran at 6 miles/hr with 0.5% incline. Not terrible, but found needing more and more time to recover heartrate back to around 130s. So dropped. RPE 6.5
 2nd set: Ran at 5.8 miles/hr with 0.5% incline. Felt better. RPE 6.5
 3rd set: Ran at 5.8 miles/hr with 0% incline. Stress felt similar to RPE 6.5
+Added 2 min at 5k. RPE 6.5
 After each run, jogged at 3 miles/hr for 2min 20 sec.
 Between each set jogged at 3 miles/hr for almost 4 min.</t>
   </si>

--- a/Marathon_Training_Log.xlsx
+++ b/Marathon_Training_Log.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Coursework\24-Git_Projects\02-Marathon_Training_Personal\Marathon_Training\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A57E01A7-8299-47B1-9FCB-BE8E7ACECBFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{232A1A6D-5EE1-403A-B242-16392C075236}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Weekly Summary" sheetId="2" r:id="rId2"/>
     <sheet name="Session Guide" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -37,8 +37,42 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="Q5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t>Optional. For sessions with a hard/easy split (strides, hill blasts): log the RPE felt during the work bouts here. Leave blank for continuous-effort sessions where the single RPE / Felt column already covers it.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="R5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t>Optional. Pairs with RPE - Work. Log how the recovery/jog portions felt here (e.g. HR dropping back below a threshold each time = low recovery RPE, a good sign).</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="119">
   <si>
     <t>Marathon Training Log — Pre-Super Base</t>
   </si>
@@ -94,6 +128,12 @@
     <t>Notes</t>
   </si>
   <si>
+    <t>RPE - Work (1-10)</t>
+  </si>
+  <si>
+    <t>RPE - Recovery (1-10)</t>
+  </si>
+  <si>
     <t>Mon</t>
   </si>
   <si>
@@ -119,150 +159,6 @@
   </si>
   <si>
     <t>KEY: WU + 3x(5x20s @ 5K effort, jog back) w/ 3 min jog between sets + CD</t>
-  </si>
-  <si>
-    <t>Planned</t>
-  </si>
-  <si>
-    <t>Wed</t>
-  </si>
-  <si>
-    <t>Rest</t>
-  </si>
-  <si>
-    <t>Rest / cross-train (easy bike/swim optional)</t>
-  </si>
-  <si>
-    <t>Thu</t>
-  </si>
-  <si>
-    <t>Easy run 45-50 min (or rest if legs heavy from Tue)</t>
-  </si>
-  <si>
-    <t>Fri</t>
-  </si>
-  <si>
-    <t>Key – Hills</t>
-  </si>
-  <si>
-    <t>KEY: WU + drills + 4x 8-sec blasts (2:30 min walk recovery)</t>
-  </si>
-  <si>
-    <t>Sat</t>
-  </si>
-  <si>
-    <t>Long</t>
-  </si>
-  <si>
-    <t>Long run 90 min easy — no tempo, conversational</t>
-  </si>
-  <si>
-    <t>Sun</t>
-  </si>
-  <si>
-    <t>KEY: WU + 3x(5x30s @ 5K effort, jog back) w/ 3 min jog between sets + CD</t>
-  </si>
-  <si>
-    <t>Easy run 45-50 min (or rest if legs heavy from Wed)</t>
-  </si>
-  <si>
-    <t>Key – Hills+Long</t>
-  </si>
-  <si>
-    <t>KEY: WU + drills + 4x 8-sec blasts (2:30 min walk recovery) — film your form  |  + Long run 90 min easy</t>
-  </si>
-  <si>
-    <t>KEY: WU + 3x(5x40s @ 5K effort, jog back) w/ 3 min jog between sets + CD</t>
-  </si>
-  <si>
-    <t>KEY: WU + drills + 6x 8-sec blasts (2:30 min walk recovery)  |  + Long run 90 min easy</t>
-  </si>
-  <si>
-    <t>KEY: WU + 3x(5x40s) + 3 min jog + 2 min @ 5K effort add-on + CD</t>
-  </si>
-  <si>
-    <t>KEY: WU + 3x(5x40s) + 3 min jog + 3 min @ 5K effort add-on + CD</t>
-  </si>
-  <si>
-    <t>KEY: WU + drills + 8x 8-sec blasts (2:30 min walk recovery)  |  + Long run 90 min easy</t>
-  </si>
-  <si>
-    <t>KEY: WU + 3x(5x40s) + 3 min jog + 4 min @ 5K effort add-on + CD</t>
-  </si>
-  <si>
-    <t>KEY: WU + 3x(5x40s) + 3 min jog + 5 min @ 5K effort add-on + CD (peak session)</t>
-  </si>
-  <si>
-    <t>KEY: Repeat: WU + 3x(5x40s) + 3 min jog + 5 min add-on + CD (consolidate — form dialled in)</t>
-  </si>
-  <si>
-    <t>Weekly Summary</t>
-  </si>
-  <si>
-    <t>Auto-calculated from the Log sheet — nothing to fill in here.</t>
-  </si>
-  <si>
-    <t>Sessions Logged</t>
-  </si>
-  <si>
-    <t>Total Actual Minutes</t>
-  </si>
-  <si>
-    <t>Total Distance (mi)</t>
-  </si>
-  <si>
-    <t>Avg RPE</t>
-  </si>
-  <si>
-    <t>Block total</t>
-  </si>
-  <si>
-    <t>Session Guide — Pre-Super Base (Stablemaster's Method)</t>
-  </si>
-  <si>
-    <t>Quick reference. Full detail lives in your Foundation &amp; Pre-Super Base workbook's Workout Library tab.</t>
-  </si>
-  <si>
-    <t>Easy Run (Mon, 65 min)</t>
-  </si>
-  <si>
-    <t>Conversational effort, full sentences, nose-breathing if possible. Peloton: any easy/'fun run' or Zone 2 tread class of matching length — ignore output/pace pushes, run by feel.</t>
-  </si>
-  <si>
-    <t>Easy Run (Thu, 45-50 min)</t>
-  </si>
-  <si>
-    <t>Same easy effort, shorter. Skip or shorten if legs are heavy from Tue strides or the upcoming Fri hill session.</t>
-  </si>
-  <si>
-    <t>Aerobic Strides (Tue, KEY)</t>
-  </si>
-  <si>
-    <t>Reps at ~5K effort to a landmark, jog back, big recovery between sets. Peloton: use a class for the warm-up/cool-down only, then pause it and self-control the treadmill for the rep timing — no canned class matches this exact protocol.</t>
-  </si>
-  <si>
-    <t>Hill Blasts (Fri or Sat, KEY)</t>
-  </si>
-  <si>
-    <t>8-sec near-max effort on a shallow incline (~5%), 2:30 WALK recovery between reps. Mantra: tall / relaxed / piston / pop. Week 1: Friday (own day). From week 2 on: same day as the long run (Saturday), done first, before the long run. Peloton: use a class for warm-up music/voice, then pause it and control incline/timing yourself — no canned class matches this protocol.</t>
-  </si>
-  <si>
-    <t>Long Run (Saturday, 90 min)</t>
-  </si>
-  <si>
-    <t>Anchored on Saturday every week per your preference. Stays at 90 min all block — easy, conversational, no tempo. From week 2 on it follows straight after hill blasts on the same day; week 1 only, it's a standalone Saturday session since hill blasts landed on Friday that week. Great one to run alongside a full-length Peloton easy/scenic tread class.</t>
-  </si>
-  <si>
-    <t>Rest / Cross-train</t>
-  </si>
-  <si>
-    <t>Full rest, walk, or easy low-impact cardio (bike/swim). Never turn it into a secret run.</t>
-  </si>
-  <si>
-    <t>Effort guide</t>
-  </si>
-  <si>
-    <t>There are no pace targets in this block by design — run everything by feel. Pace/HR should be LOGGED for your own trend-tracking, not used as a target.</t>
   </si>
   <si>
     <t>10 min Pre-Run Warm Up + 45 min Marathon Race Prep (Becs Gentry) followed by 5 min stretch.</t>
@@ -276,82 +172,133 @@
 Used treadmill.</t>
   </si>
   <si>
+    <t>Wed</t>
+  </si>
+  <si>
+    <t>Rest</t>
+  </si>
+  <si>
+    <t>Rest / cross-train (easy bike/swim optional)</t>
+  </si>
+  <si>
     <t>30 min Strength for Runners with Andy Speer</t>
   </si>
   <si>
     <t>Strength training for runners. Used 15 lb dumbell pair. Not overloading.</t>
   </si>
   <si>
+    <t>Thu</t>
+  </si>
+  <si>
+    <t>Easy run 45-50 min (or rest if legs heavy from Tue)</t>
+  </si>
+  <si>
     <t>30 min Pop Run with Selena Samuela + Apple Run for 15 min</t>
   </si>
   <si>
     <t>Easy run. Did some minor pushes inadvertently. Still felt good with nose breathing for most part. Last 15 min walked more due to incline.</t>
   </si>
   <si>
+    <t>Fri</t>
+  </si>
+  <si>
+    <t>Key – Hills</t>
+  </si>
+  <si>
+    <t>KEY: WU + drills + 4x 8-sec blasts (2:30 min walk recovery)</t>
+  </si>
+  <si>
     <t>20 min Advanced Beginner Run with Olivia Amato + 20 min total Apple workout + cooldown + stretching</t>
   </si>
   <si>
     <t>Coupled easy run as warmup then performed the drills for Hill Blast.</t>
   </si>
   <si>
+    <t>Sat</t>
+  </si>
+  <si>
+    <t>Long</t>
+  </si>
+  <si>
+    <t>Long run 90 min easy — no tempo, conversational</t>
+  </si>
+  <si>
     <t>Tracked via Apple Watch + 10 min warmup class</t>
   </si>
   <si>
     <t>Easy run. Heart rate still climed up, but the occasional walks helped heart rate to come down. Forgot headphones that did cause some unease.</t>
   </si>
   <si>
+    <t>Sun</t>
+  </si>
+  <si>
     <t xml:space="preserve">Walk </t>
   </si>
   <si>
+    <t>Modified</t>
+  </si>
+  <si>
     <t>Long walk with the dog to move around. No exersion at all.</t>
   </si>
   <si>
+    <t>30 min Strength for funners with Rebecca Kennedy</t>
+  </si>
+  <si>
+    <t>Strength training</t>
+  </si>
+  <si>
+    <t>45 min Tempo Run with Becs Gentry  + 20 min run</t>
+  </si>
+  <si>
+    <t>Nose breathing run</t>
+  </si>
+  <si>
+    <t>KEY: WU + 3x(5x30s @ 5K effort, jog back) w/ 3 min jog between sets + CD</t>
+  </si>
+  <si>
+    <t>45 min Marathon Race Prep with Robin Arzon + 10 min Pre run warmup</t>
+  </si>
+  <si>
+    <t>Night walk</t>
+  </si>
+  <si>
+    <t>Just walk</t>
+  </si>
+  <si>
+    <t>Easy run 45-50 min (or rest if legs heavy from Wed)</t>
+  </si>
+  <si>
+    <t>30 min 2010s Run with Adrian Williams + 20 min run</t>
+  </si>
+  <si>
+    <t>Key – Hills+Long</t>
+  </si>
+  <si>
+    <t>KEY: WU + drills + 4x 8-sec blasts (2:30 min walk recovery) — film your form  |  + Long run 90 min easy</t>
+  </si>
+  <si>
+    <t>Did striders on Saturday bur un on 10AUG2026 Monday</t>
+  </si>
+  <si>
+    <t>Just did striders. Actual long run done on 10AUG2026 Monday.</t>
+  </si>
+  <si>
+    <t>Rested</t>
+  </si>
+  <si>
+    <t>Did long run this day.</t>
+  </si>
+  <si>
+    <t>Saturdays long run done this day. Too much hilly route. Definitely had to slow down.</t>
+  </si>
+  <si>
     <t>Combination of 45 min Tempo Run with Becs Gentry + 10 min Pre-Run Warm Up with Matt Wilpers + 10 min cooldown</t>
   </si>
   <si>
     <t>Actual run excluding WU and CD to be 45 matchign class. Distance 3.79 miles. Running behind by 1 day.</t>
   </si>
   <si>
-    <t>Did striders on Saturday bur un on 10AUG2026 Monday</t>
-  </si>
-  <si>
-    <t>Did long run this day.</t>
-  </si>
-  <si>
-    <t>30 min 2010s Run with Adrian Williams + 20 min run</t>
-  </si>
-  <si>
-    <t>45 min Marathon Race Prep with Robin Arzon + 10 min Pre run warmup</t>
-  </si>
-  <si>
-    <t>45 min Tempo Run with Becs Gentry  + 20 min run</t>
-  </si>
-  <si>
-    <t>30 min Strength for funners with Rebecca Kennedy</t>
-  </si>
-  <si>
-    <t>Strength training</t>
-  </si>
-  <si>
-    <t>Nose breathing run</t>
-  </si>
-  <si>
-    <t>Night walk</t>
-  </si>
-  <si>
-    <t>Just walk</t>
-  </si>
-  <si>
-    <t>Rested</t>
-  </si>
-  <si>
-    <t>Saturdays long run done this day. Too much hilly route. Definitely had to slow down.</t>
-  </si>
-  <si>
-    <t>Modified</t>
-  </si>
-  <si>
-    <t>Just did striders. Actual long run done on 10AUG2026 Monday.</t>
+    <t>KEY: WU + 3x(5x40s @ 5K effort, jog back) w/ 3 min jog between sets + CD</t>
   </si>
   <si>
     <t>10 min Pre-Run Warm Up with Becs Gentry + 34 min Marathon Race Prep with Matt Wilpers + Night Run</t>
@@ -366,6 +313,9 @@
     <t>Took rest to reset schedule and have long run on Saturday.</t>
   </si>
   <si>
+    <t>KEY: WU + drills + 6x 8-sec blasts (2:30 min walk recovery)  |  + Long run 90 min easy</t>
+  </si>
+  <si>
     <t>10 min long run warm up with robin arzon + Hill blasts + 90 min Evening Run</t>
   </si>
   <si>
@@ -388,6 +338,9 @@
   </si>
   <si>
     <t>Very slow running. Did hit some hills so heart rate spiked during that time. But mostly the heart rate was below 148 bpm.</t>
+  </si>
+  <si>
+    <t>KEY: WU + 3x(5x40s) + 3 min jog + 2 min @ 5K effort add-on + CD</t>
   </si>
   <si>
     <t>15 min warmup + 45 min Tempo Run with Becs Gentry + 10 min coolodown</t>
@@ -398,9 +351,95 @@
 1st set: Ran at 6 miles/hr with 0.5% incline. Not terrible, but found needing more and more time to recover heartrate back to around 130s. So dropped. RPE 6.5
 2nd set: Ran at 5.8 miles/hr with 0.5% incline. Felt better. RPE 6.5
 3rd set: Ran at 5.8 miles/hr with 0% incline. Stress felt similar to RPE 6.5
-Added 2 min at 5k. RPE 6.5
 After each run, jogged at 3 miles/hr for 2min 20 sec.
 Between each set jogged at 3 miles/hr for almost 4 min.</t>
+  </si>
+  <si>
+    <t>Planned</t>
+  </si>
+  <si>
+    <t>KEY: WU + 3x(5x40s) + 3 min jog + 3 min @ 5K effort add-on + CD</t>
+  </si>
+  <si>
+    <t>KEY: WU + drills + 8x 8-sec blasts (2:30 min walk recovery)  |  + Long run 90 min easy</t>
+  </si>
+  <si>
+    <t>KEY: WU + 3x(5x40s) + 3 min jog + 4 min @ 5K effort add-on + CD</t>
+  </si>
+  <si>
+    <t>KEY: WU + 3x(5x40s) + 3 min jog + 5 min @ 5K effort add-on + CD (peak session)</t>
+  </si>
+  <si>
+    <t>KEY: Repeat: WU + 3x(5x40s) + 3 min jog + 5 min add-on + CD (consolidate — form dialled in)</t>
+  </si>
+  <si>
+    <t>Weekly Summary</t>
+  </si>
+  <si>
+    <t>Auto-calculated from the Log sheet — nothing to fill in here.</t>
+  </si>
+  <si>
+    <t>Sessions Logged</t>
+  </si>
+  <si>
+    <t>Total Actual Minutes</t>
+  </si>
+  <si>
+    <t>Total Distance (mi)</t>
+  </si>
+  <si>
+    <t>Avg RPE</t>
+  </si>
+  <si>
+    <t>Block total</t>
+  </si>
+  <si>
+    <t>Session Guide — Pre-Super Base (Stablemaster's Method)</t>
+  </si>
+  <si>
+    <t>Quick reference. Full detail lives in your Foundation &amp; Pre-Super Base workbook's Workout Library tab.</t>
+  </si>
+  <si>
+    <t>Easy Run (Mon, 65 min)</t>
+  </si>
+  <si>
+    <t>Conversational effort, full sentences, nose-breathing if possible. Peloton: any easy/'fun run' or Zone 2 tread class of matching length — ignore output/pace pushes, run by feel.</t>
+  </si>
+  <si>
+    <t>Easy Run (Thu, 45-50 min)</t>
+  </si>
+  <si>
+    <t>Same easy effort, shorter. Skip or shorten if legs are heavy from Tue strides or the upcoming Fri hill session.</t>
+  </si>
+  <si>
+    <t>Aerobic Strides (Tue, KEY)</t>
+  </si>
+  <si>
+    <t>Reps at ~5K effort to a landmark, jog back, big recovery between sets. Peloton: use a class for the warm-up/cool-down only, then pause it and self-control the treadmill for the rep timing — no canned class matches this exact protocol.</t>
+  </si>
+  <si>
+    <t>Hill Blasts (Fri or Sat, KEY)</t>
+  </si>
+  <si>
+    <t>8-sec near-max effort on a shallow incline (~5%), 2:30 WALK recovery between reps. Mantra: tall / relaxed / piston / pop. Week 1: Friday (own day). From week 2 on: same day as the long run (Saturday), done first, before the long run. Peloton: use a class for warm-up music/voice, then pause it and control incline/timing yourself — no canned class matches this protocol.</t>
+  </si>
+  <si>
+    <t>Long Run (Saturday, 90 min)</t>
+  </si>
+  <si>
+    <t>Anchored on Saturday every week per your preference. Stays at 90 min all block — easy, conversational, no tempo. From week 2 on it follows straight after hill blasts on the same day; week 1 only, it's a standalone Saturday session since hill blasts landed on Friday that week. Great one to run alongside a full-length Peloton easy/scenic tread class.</t>
+  </si>
+  <si>
+    <t>Rest / Cross-train</t>
+  </si>
+  <si>
+    <t>Full rest, walk, or easy low-impact cardio (bike/swim). Never turn it into a secret run.</t>
+  </si>
+  <si>
+    <t>Effort guide</t>
+  </si>
+  <si>
+    <t>There are no pace targets in this block by design — run everything by feel. Pace/HR should be LOGGED for your own trend-tracking, not used as a target.</t>
   </si>
 </sst>
 </file>
@@ -410,7 +449,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="mm/dd/yy&quot; (&quot;ddd\)"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -443,6 +482,11 @@
       <sz val="10"/>
       <name val="Arial"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -565,9 +609,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -834,8 +878,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:P61"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="B2:R61"/>
   <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="43.140625" customWidth="1"/>
@@ -850,14 +894,16 @@
     <col min="14" max="14" width="8" customWidth="1"/>
     <col min="15" max="15" width="7.140625" customWidth="1"/>
     <col min="16" max="16" width="73.5703125" customWidth="1"/>
+    <col min="17" max="17" width="20" customWidth="1"/>
+    <col min="18" max="18" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:16" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:18" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="2:16" s="2" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:18" s="2" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
@@ -865,7 +911,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="5" spans="2:16" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:18" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="4" t="s">
         <v>3</v>
       </c>
@@ -911,28 +957,34 @@
       <c r="P5" s="4" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="6" spans="2:16" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q5" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="R5" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="2:18" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="5">
         <v>46230</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D6" s="6">
         <v>1</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="H6" s="9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I6" s="6">
         <v>65</v>
@@ -956,30 +1008,30 @@
         <v>5</v>
       </c>
       <c r="P6" s="8" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="7" spans="2:16" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="2:18" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="10">
         <v>46231</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D7" s="11">
         <v>1</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>75</v>
+        <v>29</v>
       </c>
       <c r="H7" s="9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I7" s="11">
         <v>50</v>
@@ -1003,30 +1055,30 @@
         <v>6</v>
       </c>
       <c r="P7" s="8" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="8" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="8" spans="2:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="13">
         <v>46232</v>
       </c>
       <c r="C8" s="14" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D8" s="14">
         <v>1</v>
       </c>
       <c r="E8" s="14" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F8" s="15" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>77</v>
+        <v>34</v>
       </c>
       <c r="H8" s="9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I8" s="14">
         <v>0</v>
@@ -1050,30 +1102,30 @@
         <v>4</v>
       </c>
       <c r="P8" s="8" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="9" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9" spans="2:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="5">
         <v>46233</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D9" s="6">
         <v>1</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>79</v>
+        <v>38</v>
       </c>
       <c r="H9" s="9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I9" s="6">
         <v>50</v>
@@ -1097,30 +1149,30 @@
         <v>5</v>
       </c>
       <c r="P9" s="8" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="10" spans="2:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="10" spans="2:18" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B10" s="10">
         <v>46234</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D10" s="11">
         <v>1</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>81</v>
+        <v>43</v>
       </c>
       <c r="H10" s="9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I10" s="11">
         <v>45</v>
@@ -1144,30 +1196,30 @@
         <v>4</v>
       </c>
       <c r="P10" s="8" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="11" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="2:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="10">
         <v>46235</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="D11" s="11">
         <v>1</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>37</v>
+        <v>46</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>83</v>
+        <v>48</v>
       </c>
       <c r="H11" s="9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I11" s="11">
         <v>90</v>
@@ -1191,30 +1243,30 @@
         <v>5</v>
       </c>
       <c r="P11" s="8" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="12" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="12" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B12" s="13">
         <v>46236</v>
       </c>
       <c r="C12" s="14" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="D12" s="14">
         <v>1</v>
       </c>
       <c r="E12" s="14" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F12" s="15" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>85</v>
+        <v>51</v>
       </c>
       <c r="H12" s="9" t="s">
-        <v>101</v>
+        <v>52</v>
       </c>
       <c r="I12" s="14">
         <v>0</v>
@@ -1238,30 +1290,36 @@
         <v>2</v>
       </c>
       <c r="P12" s="8" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="13" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>53</v>
+      </c>
+      <c r="Q12">
+        <v>2</v>
+      </c>
+      <c r="R12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="2:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="13">
         <v>46237</v>
       </c>
       <c r="C13" s="14" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D13" s="14">
         <v>2</v>
       </c>
       <c r="E13" s="14" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>94</v>
+        <v>54</v>
       </c>
       <c r="H13" s="9" t="s">
-        <v>101</v>
+        <v>52</v>
       </c>
       <c r="I13" s="14">
         <v>0</v>
@@ -1285,30 +1343,36 @@
         <v>3</v>
       </c>
       <c r="P13" s="8" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="14" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>55</v>
+      </c>
+      <c r="Q13">
+        <v>3</v>
+      </c>
+      <c r="R13">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="2:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="5">
         <v>46238</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D14" s="6">
         <v>2</v>
       </c>
       <c r="E14" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F14" s="7" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>93</v>
+        <v>56</v>
       </c>
       <c r="H14" s="9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I14" s="6">
         <v>65</v>
@@ -1332,30 +1396,36 @@
         <v>5</v>
       </c>
       <c r="P14" s="8" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="15" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+      <c r="Q14">
+        <v>5</v>
+      </c>
+      <c r="R14">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="15" spans="2:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="10">
         <v>46239</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D15" s="11">
         <v>2</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="G15" s="8" t="s">
-        <v>92</v>
+        <v>59</v>
       </c>
       <c r="H15" s="9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I15" s="11">
         <v>52</v>
@@ -1379,30 +1449,36 @@
         <v>5</v>
       </c>
       <c r="P15" s="8" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="16" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>57</v>
+      </c>
+      <c r="Q15">
+        <v>5</v>
+      </c>
+      <c r="R15">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="2:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="13">
         <v>46240</v>
       </c>
       <c r="C16" s="14" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D16" s="14">
         <v>2</v>
       </c>
       <c r="E16" s="14" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F16" s="15" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G16" s="8" t="s">
-        <v>97</v>
+        <v>60</v>
       </c>
       <c r="H16" s="9" t="s">
-        <v>101</v>
+        <v>52</v>
       </c>
       <c r="I16" s="14">
         <v>0</v>
@@ -1424,30 +1500,36 @@
         <v>2</v>
       </c>
       <c r="P16" s="8" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="17" spans="2:16" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+      <c r="Q16">
+        <v>2</v>
+      </c>
+      <c r="R16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="2:18" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="5">
         <v>46241</v>
       </c>
       <c r="C17" s="6" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D17" s="6">
         <v>2</v>
       </c>
       <c r="E17" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F17" s="7" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="G17" s="8" t="s">
-        <v>91</v>
+        <v>63</v>
       </c>
       <c r="H17" s="9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I17" s="6">
         <v>50</v>
@@ -1471,28 +1553,34 @@
         <v>5</v>
       </c>
       <c r="P17" s="8"/>
-    </row>
-    <row r="18" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q17">
+        <v>5</v>
+      </c>
+      <c r="R17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18" spans="2:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B18" s="10">
         <v>46242</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="D18" s="11">
         <v>2</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>43</v>
+        <v>65</v>
       </c>
       <c r="G18" s="8" t="s">
-        <v>89</v>
+        <v>66</v>
       </c>
       <c r="H18" s="9" t="s">
-        <v>101</v>
+        <v>52</v>
       </c>
       <c r="I18" s="11">
         <v>135</v>
@@ -1516,30 +1604,36 @@
         <v>5</v>
       </c>
       <c r="P18" s="8" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="19" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>67</v>
+      </c>
+      <c r="Q18">
+        <v>5</v>
+      </c>
+      <c r="R18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="13">
         <v>46243</v>
       </c>
       <c r="C19" s="14" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="D19" s="14">
         <v>2</v>
       </c>
       <c r="E19" s="14" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F19" s="15" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G19" s="8" t="s">
-        <v>99</v>
+        <v>68</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I19" s="14">
         <v>0</v>
@@ -1563,28 +1657,34 @@
         <v>0</v>
       </c>
       <c r="P19" s="8"/>
-    </row>
-    <row r="20" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="Q19">
+        <v>0</v>
+      </c>
+      <c r="R19">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="2:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B20" s="13">
         <v>46244</v>
       </c>
       <c r="C20" s="14" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D20" s="14">
         <v>3</v>
       </c>
       <c r="E20" s="14" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G20" s="8" t="s">
-        <v>90</v>
+        <v>69</v>
       </c>
       <c r="H20" s="9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I20" s="14">
         <v>0</v>
@@ -1608,30 +1708,36 @@
         <v>5</v>
       </c>
       <c r="P20" s="8" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="21" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>70</v>
+      </c>
+      <c r="Q20">
+        <v>5</v>
+      </c>
+      <c r="R20">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="2:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B21" s="5">
         <v>46245</v>
       </c>
       <c r="C21" s="6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D21" s="6">
         <v>3</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F21" s="7" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G21" s="8" t="s">
-        <v>87</v>
+        <v>71</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I21" s="6">
         <v>65</v>
@@ -1655,30 +1761,36 @@
         <v>5</v>
       </c>
       <c r="P21" s="8" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="22" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>72</v>
+      </c>
+      <c r="Q21">
+        <v>5</v>
+      </c>
+      <c r="R21">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="2:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B22" s="10">
         <v>46246</v>
       </c>
       <c r="C22" s="11" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D22" s="11">
         <v>3</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>44</v>
+        <v>73</v>
       </c>
       <c r="G22" s="8" t="s">
-        <v>103</v>
+        <v>74</v>
       </c>
       <c r="H22" s="9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I22" s="11">
         <v>55</v>
@@ -1702,28 +1814,34 @@
         <v>7</v>
       </c>
       <c r="P22" s="8" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="23" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>75</v>
+      </c>
+      <c r="Q22">
+        <v>7</v>
+      </c>
+      <c r="R22">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="23" spans="2:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="13">
         <v>46247</v>
       </c>
       <c r="C23" s="14" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D23" s="14">
         <v>3</v>
       </c>
       <c r="E23" s="14" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F23" s="15" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G23" s="8"/>
       <c r="H23" s="9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I23" s="14">
         <v>0</v>
@@ -1747,28 +1865,34 @@
         <v>0</v>
       </c>
       <c r="P23" s="8" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="24" spans="2:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+      <c r="Q23">
+        <v>0</v>
+      </c>
+      <c r="R23">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="2:18" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="5">
         <v>46248</v>
       </c>
       <c r="C24" s="6" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D24" s="6">
         <v>3</v>
       </c>
       <c r="E24" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F24" s="7" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="G24" s="8"/>
       <c r="H24" s="9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I24" s="6">
         <v>50</v>
@@ -1792,30 +1916,36 @@
         <v>0</v>
       </c>
       <c r="P24" s="8" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="25" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>77</v>
+      </c>
+      <c r="Q24">
+        <v>0</v>
+      </c>
+      <c r="R24">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="2:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B25" s="10">
         <v>46249</v>
       </c>
       <c r="C25" s="11" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="D25" s="11">
         <v>3</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="G25" s="8" t="s">
-        <v>107</v>
+        <v>79</v>
       </c>
       <c r="H25" s="9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I25" s="11">
         <v>140</v>
@@ -1839,30 +1969,36 @@
         <v>3</v>
       </c>
       <c r="P25" s="8" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="26" spans="2:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>80</v>
+      </c>
+      <c r="Q25">
+        <v>3</v>
+      </c>
+      <c r="R25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="2:18" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B26" s="13">
         <v>46250</v>
       </c>
       <c r="C26" s="14" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="D26" s="14">
         <v>3</v>
       </c>
       <c r="E26" s="14" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F26" s="15" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G26" s="8" t="s">
-        <v>109</v>
+        <v>81</v>
       </c>
       <c r="H26" s="9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I26" s="14">
         <v>0</v>
@@ -1886,30 +2022,36 @@
         <v>1</v>
       </c>
       <c r="P26" s="8" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="27" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>82</v>
+      </c>
+      <c r="Q26">
+        <v>1</v>
+      </c>
+      <c r="R26">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="2:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B27" s="13">
         <v>46251</v>
       </c>
       <c r="C27" s="14" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D27" s="14">
         <v>4</v>
       </c>
       <c r="E27" s="14" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F27" s="15" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G27" s="8" t="s">
-        <v>111</v>
+        <v>83</v>
       </c>
       <c r="H27" s="9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I27" s="14">
         <v>0</v>
@@ -1933,30 +2075,36 @@
         <v>3</v>
       </c>
       <c r="P27" s="8" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="28" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>84</v>
+      </c>
+      <c r="Q27">
+        <v>3</v>
+      </c>
+      <c r="R27">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="28" spans="2:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B28" s="5">
         <v>46252</v>
       </c>
       <c r="C28" s="6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D28" s="6">
         <v>4</v>
       </c>
       <c r="E28" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G28" s="8" t="s">
-        <v>113</v>
+        <v>85</v>
       </c>
       <c r="H28" s="9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I28" s="6">
         <v>65</v>
@@ -1980,30 +2128,36 @@
         <v>3.5</v>
       </c>
       <c r="P28" s="8" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="29" spans="2:16" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>86</v>
+      </c>
+      <c r="Q28">
+        <v>3.5</v>
+      </c>
+      <c r="R28">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="29" spans="2:18" ht="98.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B29" s="10">
         <v>46253</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D29" s="11">
         <v>4</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>46</v>
+        <v>87</v>
       </c>
       <c r="G29" s="8" t="s">
-        <v>115</v>
+        <v>88</v>
       </c>
       <c r="H29" s="9" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="I29" s="11">
         <v>57</v>
@@ -2027,28 +2181,34 @@
         <v>6.5</v>
       </c>
       <c r="P29" s="8" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="30" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+        <v>89</v>
+      </c>
+      <c r="Q29">
+        <v>6.5</v>
+      </c>
+      <c r="R29">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="30" spans="2:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B30" s="13">
         <v>46254</v>
       </c>
       <c r="C30" s="14" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D30" s="14">
         <v>4</v>
       </c>
       <c r="E30" s="14" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F30" s="15" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G30" s="8"/>
       <c r="H30" s="9" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="I30" s="14">
         <v>0</v>
@@ -2061,25 +2221,25 @@
       <c r="O30" s="9"/>
       <c r="P30" s="8"/>
     </row>
-    <row r="31" spans="2:16" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:18" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B31" s="5">
         <v>46255</v>
       </c>
       <c r="C31" s="6" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D31" s="6">
         <v>4</v>
       </c>
       <c r="E31" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="G31" s="8"/>
       <c r="H31" s="9" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="I31" s="6">
         <v>50</v>
@@ -2092,25 +2252,25 @@
       <c r="O31" s="9"/>
       <c r="P31" s="8"/>
     </row>
-    <row r="32" spans="2:16" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B32" s="10">
         <v>46256</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="D32" s="11">
         <v>4</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="F32" s="12" t="s">
-        <v>45</v>
+        <v>78</v>
       </c>
       <c r="G32" s="8"/>
       <c r="H32" s="9" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="I32" s="11">
         <v>140</v>
@@ -2128,20 +2288,20 @@
         <v>46257</v>
       </c>
       <c r="C33" s="14" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="D33" s="14">
         <v>4</v>
       </c>
       <c r="E33" s="14" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F33" s="15" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G33" s="8"/>
       <c r="H33" s="9" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="I33" s="14">
         <v>0</v>
@@ -2159,20 +2319,20 @@
         <v>46258</v>
       </c>
       <c r="C34" s="14" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D34" s="14">
         <v>5</v>
       </c>
       <c r="E34" s="14" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F34" s="15" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G34" s="8"/>
       <c r="H34" s="9" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="I34" s="14">
         <v>0</v>
@@ -2190,20 +2350,20 @@
         <v>46259</v>
       </c>
       <c r="C35" s="6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D35" s="6">
         <v>5</v>
       </c>
       <c r="E35" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G35" s="8"/>
       <c r="H35" s="9" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="I35" s="6">
         <v>65</v>
@@ -2221,20 +2381,20 @@
         <v>46260</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D36" s="11">
         <v>5</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F36" s="12" t="s">
-        <v>47</v>
+        <v>91</v>
       </c>
       <c r="G36" s="8"/>
       <c r="H36" s="9" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="I36" s="11">
         <v>58</v>
@@ -2252,20 +2412,20 @@
         <v>46261</v>
       </c>
       <c r="C37" s="14" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D37" s="14">
         <v>5</v>
       </c>
       <c r="E37" s="14" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F37" s="15" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G37" s="8"/>
       <c r="H37" s="9" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="I37" s="14">
         <v>0</v>
@@ -2283,20 +2443,20 @@
         <v>46262</v>
       </c>
       <c r="C38" s="6" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D38" s="6">
         <v>5</v>
       </c>
       <c r="E38" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F38" s="7" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="G38" s="8"/>
       <c r="H38" s="9" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="I38" s="6">
         <v>50</v>
@@ -2314,20 +2474,20 @@
         <v>46263</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="D39" s="11">
         <v>5</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="F39" s="12" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="G39" s="8"/>
       <c r="H39" s="9" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="I39" s="11">
         <v>145</v>
@@ -2345,20 +2505,20 @@
         <v>46264</v>
       </c>
       <c r="C40" s="14" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="D40" s="14">
         <v>5</v>
       </c>
       <c r="E40" s="14" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F40" s="15" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G40" s="8"/>
       <c r="H40" s="9" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="I40" s="14">
         <v>0</v>
@@ -2376,20 +2536,20 @@
         <v>46265</v>
       </c>
       <c r="C41" s="14" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D41" s="14">
         <v>6</v>
       </c>
       <c r="E41" s="14" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F41" s="15" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G41" s="8"/>
       <c r="H41" s="9" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="I41" s="14">
         <v>0</v>
@@ -2407,20 +2567,20 @@
         <v>46266</v>
       </c>
       <c r="C42" s="6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D42" s="6">
         <v>6</v>
       </c>
       <c r="E42" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F42" s="7" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G42" s="8"/>
       <c r="H42" s="9" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="I42" s="6">
         <v>65</v>
@@ -2438,20 +2598,20 @@
         <v>46267</v>
       </c>
       <c r="C43" s="11" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D43" s="11">
         <v>6</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F43" s="12" t="s">
-        <v>49</v>
+        <v>93</v>
       </c>
       <c r="G43" s="8"/>
       <c r="H43" s="9" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="I43" s="11">
         <v>59</v>
@@ -2469,20 +2629,20 @@
         <v>46268</v>
       </c>
       <c r="C44" s="14" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D44" s="14">
         <v>6</v>
       </c>
       <c r="E44" s="14" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F44" s="15" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G44" s="8"/>
       <c r="H44" s="9" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="I44" s="14">
         <v>0</v>
@@ -2500,20 +2660,20 @@
         <v>46269</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D45" s="6">
         <v>6</v>
       </c>
       <c r="E45" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F45" s="7" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="G45" s="8"/>
       <c r="H45" s="9" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="I45" s="6">
         <v>50</v>
@@ -2531,20 +2691,20 @@
         <v>46270</v>
       </c>
       <c r="C46" s="11" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="D46" s="11">
         <v>6</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="F46" s="12" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="G46" s="8"/>
       <c r="H46" s="9" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="I46" s="11">
         <v>145</v>
@@ -2562,20 +2722,20 @@
         <v>46271</v>
       </c>
       <c r="C47" s="14" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="D47" s="14">
         <v>6</v>
       </c>
       <c r="E47" s="14" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F47" s="15" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G47" s="8"/>
       <c r="H47" s="9" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="I47" s="14">
         <v>0</v>
@@ -2593,20 +2753,20 @@
         <v>46272</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D48" s="14">
         <v>7</v>
       </c>
       <c r="E48" s="14" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F48" s="15" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G48" s="8"/>
       <c r="H48" s="9" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="I48" s="14">
         <v>0</v>
@@ -2624,20 +2784,20 @@
         <v>46273</v>
       </c>
       <c r="C49" s="6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D49" s="6">
         <v>7</v>
       </c>
       <c r="E49" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F49" s="7" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G49" s="8"/>
       <c r="H49" s="9" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="I49" s="6">
         <v>65</v>
@@ -2655,20 +2815,20 @@
         <v>46274</v>
       </c>
       <c r="C50" s="11" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D50" s="11">
         <v>7</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F50" s="12" t="s">
-        <v>50</v>
+        <v>94</v>
       </c>
       <c r="G50" s="8"/>
       <c r="H50" s="9" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="I50" s="11">
         <v>60</v>
@@ -2686,20 +2846,20 @@
         <v>46275</v>
       </c>
       <c r="C51" s="14" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D51" s="14">
         <v>7</v>
       </c>
       <c r="E51" s="14" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F51" s="15" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G51" s="8"/>
       <c r="H51" s="9" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="I51" s="14">
         <v>0</v>
@@ -2717,20 +2877,20 @@
         <v>46276</v>
       </c>
       <c r="C52" s="6" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D52" s="6">
         <v>7</v>
       </c>
       <c r="E52" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F52" s="7" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="G52" s="8"/>
       <c r="H52" s="9" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="I52" s="6">
         <v>50</v>
@@ -2748,20 +2908,20 @@
         <v>46277</v>
       </c>
       <c r="C53" s="11" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="D53" s="11">
         <v>7</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="F53" s="12" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="G53" s="8"/>
       <c r="H53" s="9" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="I53" s="11">
         <v>145</v>
@@ -2779,20 +2939,20 @@
         <v>46278</v>
       </c>
       <c r="C54" s="14" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="D54" s="14">
         <v>7</v>
       </c>
       <c r="E54" s="14" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F54" s="15" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G54" s="8"/>
       <c r="H54" s="9" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="I54" s="14">
         <v>0</v>
@@ -2810,20 +2970,20 @@
         <v>46279</v>
       </c>
       <c r="C55" s="14" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="D55" s="14">
         <v>8</v>
       </c>
       <c r="E55" s="14" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F55" s="15" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G55" s="8"/>
       <c r="H55" s="9" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="I55" s="14">
         <v>0</v>
@@ -2841,20 +3001,20 @@
         <v>46280</v>
       </c>
       <c r="C56" s="6" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="D56" s="6">
         <v>8</v>
       </c>
       <c r="E56" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F56" s="7" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G56" s="8"/>
       <c r="H56" s="9" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="I56" s="6">
         <v>65</v>
@@ -2872,20 +3032,20 @@
         <v>46281</v>
       </c>
       <c r="C57" s="11" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D57" s="11">
         <v>8</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F57" s="12" t="s">
-        <v>51</v>
+        <v>95</v>
       </c>
       <c r="G57" s="8"/>
       <c r="H57" s="9" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="I57" s="11">
         <v>60</v>
@@ -2903,20 +3063,20 @@
         <v>46282</v>
       </c>
       <c r="C58" s="14" t="s">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="D58" s="14">
         <v>8</v>
       </c>
       <c r="E58" s="14" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F58" s="15" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G58" s="8"/>
       <c r="H58" s="9" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="I58" s="14">
         <v>0</v>
@@ -2934,20 +3094,20 @@
         <v>46283</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="D59" s="6">
         <v>8</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F59" s="7" t="s">
-        <v>41</v>
+        <v>62</v>
       </c>
       <c r="G59" s="8"/>
       <c r="H59" s="9" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="I59" s="6">
         <v>50</v>
@@ -2965,20 +3125,20 @@
         <v>46284</v>
       </c>
       <c r="C60" s="11" t="s">
-        <v>36</v>
+        <v>45</v>
       </c>
       <c r="D60" s="11">
         <v>8</v>
       </c>
       <c r="E60" s="11" t="s">
-        <v>42</v>
+        <v>64</v>
       </c>
       <c r="F60" s="12" t="s">
-        <v>48</v>
+        <v>92</v>
       </c>
       <c r="G60" s="8"/>
       <c r="H60" s="9" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="I60" s="11">
         <v>145</v>
@@ -2996,20 +3156,20 @@
         <v>46285</v>
       </c>
       <c r="C61" s="14" t="s">
-        <v>39</v>
+        <v>50</v>
       </c>
       <c r="D61" s="14">
         <v>8</v>
       </c>
       <c r="E61" s="14" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F61" s="15" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G61" s="8"/>
       <c r="H61" s="9" t="s">
-        <v>27</v>
+        <v>90</v>
       </c>
       <c r="I61" s="14">
         <v>0</v>
@@ -3031,6 +3191,7 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -3047,12 +3208,12 @@
   <sheetData>
     <row r="2" spans="2:6" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
-        <v>52</v>
+        <v>96</v>
       </c>
     </row>
     <row r="3" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="16" t="s">
-        <v>53</v>
+        <v>97</v>
       </c>
     </row>
     <row r="5" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3060,16 +3221,16 @@
         <v>5</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>54</v>
+        <v>98</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>55</v>
+        <v>99</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>56</v>
+        <v>100</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>57</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3242,7 +3403,7 @@
     </row>
     <row r="14" spans="2:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="18" t="s">
-        <v>58</v>
+        <v>102</v>
       </c>
       <c r="C14" s="19">
         <f>SUM(C6:C13)</f>
@@ -3274,68 +3435,68 @@
   <sheetData>
     <row r="2" spans="2:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
-        <v>59</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="2:3" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="16" t="s">
-        <v>60</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" spans="2:3" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="20" t="s">
-        <v>61</v>
+        <v>105</v>
       </c>
       <c r="C5" s="21" t="s">
-        <v>62</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" spans="2:3" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="20" t="s">
-        <v>63</v>
+        <v>107</v>
       </c>
       <c r="C7" s="21" t="s">
-        <v>64</v>
+        <v>108</v>
       </c>
     </row>
     <row r="9" spans="2:3" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="20" t="s">
-        <v>65</v>
+        <v>109</v>
       </c>
       <c r="C9" s="21" t="s">
-        <v>66</v>
+        <v>110</v>
       </c>
     </row>
     <row r="11" spans="2:3" ht="70.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B11" s="20" t="s">
-        <v>67</v>
+        <v>111</v>
       </c>
       <c r="C11" s="21" t="s">
-        <v>68</v>
+        <v>112</v>
       </c>
     </row>
     <row r="13" spans="2:3" ht="77.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B13" s="20" t="s">
-        <v>69</v>
+        <v>113</v>
       </c>
       <c r="C13" s="21" t="s">
-        <v>70</v>
+        <v>114</v>
       </c>
     </row>
     <row r="15" spans="2:3" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="20" t="s">
-        <v>71</v>
+        <v>115</v>
       </c>
       <c r="C15" s="21" t="s">
-        <v>72</v>
+        <v>116</v>
       </c>
     </row>
     <row r="17" spans="2:3" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B17" s="20" t="s">
-        <v>73</v>
+        <v>117</v>
       </c>
       <c r="C17" s="21" t="s">
-        <v>74</v>
+        <v>118</v>
       </c>
     </row>
   </sheetData>
